--- a/config/PCS_125_英博.xlsx
+++ b/config/PCS_125_英博.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="18569" windowHeight="11268"/>
+    <workbookView windowWidth="22010" windowHeight="12332"/>
   </bookViews>
   <sheets>
     <sheet name="遥测" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="233">
   <si>
     <t>序号</t>
   </si>
@@ -66,6 +66,18 @@
   </si>
   <si>
     <t>启用</t>
+  </si>
+  <si>
+    <t>键</t>
+  </si>
+  <si>
+    <t>点位名称翻译</t>
+  </si>
+  <si>
+    <t>状态字</t>
+  </si>
+  <si>
+    <t>告警位</t>
   </si>
   <si>
     <t>PCS端口 A 相电压</t>
@@ -1357,7 +1369,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1374,9 +1386,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1910,7 +1919,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L180"/>
+  <dimension ref="A1:P180"/>
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="9.11111111111111" style="2"/>
@@ -1919,10 +1928,12 @@
     <col min="6" max="6" width="10.957264957265" style="2" customWidth="1"/>
     <col min="7" max="7" width="17.3931623931624" style="2" customWidth="1"/>
     <col min="8" max="9" width="11.7435897435897" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9.11111111111111" style="2"/>
+    <col min="10" max="13" width="9.11111111111111" style="2"/>
+    <col min="14" max="14" width="12.957264957265" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9.11111111111111" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12">
+    <row r="1" s="1" customFormat="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1959,31 +1970,43 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2">
         <v>201</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H2" s="2">
         <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J2" s="2">
         <v>0.1</v>
@@ -1992,30 +2015,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:16">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F3" s="2">
         <v>202</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H3" s="2">
         <v>1</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J3" s="2">
         <v>0.1</v>
@@ -2024,30 +2047,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:16">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="F4" s="2">
         <v>203</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H4" s="2">
         <v>1</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J4" s="2">
         <v>0.1</v>
@@ -2056,30 +2079,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:16">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F5" s="2">
         <v>204</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H5" s="2">
         <v>1</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J5" s="2">
         <v>0.1</v>
@@ -2088,30 +2111,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:16">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F6" s="2">
         <v>205</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J6" s="2">
         <v>0.1</v>
@@ -2120,30 +2143,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:16">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F7" s="2">
         <v>206</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J7" s="2">
         <v>0.1</v>
@@ -2152,30 +2175,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:16">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F8" s="2">
         <v>207</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J8" s="2">
         <v>0.01</v>
@@ -2184,30 +2207,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:16">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F9" s="2">
         <v>208</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J9" s="2">
         <v>0.1</v>
@@ -2216,30 +2239,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:16">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F10" s="2">
         <v>209</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J10" s="2">
         <v>0.1</v>
@@ -2248,30 +2271,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:16">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F11" s="2">
         <v>210</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J11" s="2">
         <v>0.1</v>
@@ -2280,30 +2303,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:16">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F12" s="2">
         <v>211</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J12" s="2">
         <v>0.1</v>
@@ -2312,30 +2335,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:16">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F13" s="2">
         <v>212</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J13" s="2">
         <v>0.1</v>
@@ -2344,30 +2367,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:16">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F14" s="2">
         <v>213</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J14" s="2">
         <v>0.1</v>
@@ -2376,30 +2399,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:16">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F15" s="2">
         <v>214</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J15" s="2">
         <v>0.1</v>
@@ -2408,30 +2431,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:16">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F16" s="2">
         <v>215</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J16" s="2">
         <v>0.1</v>
@@ -2445,25 +2468,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F17" s="2">
         <v>216</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J17" s="2">
         <v>0.1</v>
@@ -2477,25 +2500,25 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F18" s="2">
         <v>217</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J18" s="2">
         <v>0.1</v>
@@ -2509,25 +2532,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F19" s="2">
         <v>218</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J19" s="2">
         <v>0.1</v>
@@ -2541,25 +2564,25 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F20" s="2">
         <v>219</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J20" s="2">
         <v>0.1</v>
@@ -2573,22 +2596,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F21" s="2">
         <v>220</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J21" s="2">
         <v>0.001</v>
@@ -2602,22 +2625,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F22" s="2">
         <v>221</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J22" s="2">
         <v>0.001</v>
@@ -2631,22 +2654,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F23" s="2">
         <v>222</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J23" s="2">
         <v>0.001</v>
@@ -2660,22 +2683,22 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F24" s="2">
         <v>223</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J24" s="2">
         <v>0.001</v>
@@ -2689,25 +2712,25 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F25" s="2">
         <v>224</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J25" s="2">
         <v>0.1</v>
@@ -2721,25 +2744,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F26" s="2">
         <v>225</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J26" s="2">
         <v>0.1</v>
@@ -2753,25 +2776,25 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F27" s="2">
         <v>226</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J27" s="2">
         <v>0.1</v>
@@ -2785,25 +2808,25 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F28" s="2">
         <v>227</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J28" s="2">
         <v>1</v>
@@ -2817,22 +2840,22 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F29" s="2">
         <v>228</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J29" s="2">
         <v>1</v>
@@ -2846,22 +2869,22 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F30" s="2">
         <v>229</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J30" s="2">
         <v>1</v>
@@ -2875,25 +2898,25 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F31" s="2">
         <v>230</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H31" s="2">
         <v>2</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J31" s="2">
         <v>0.001</v>
@@ -2907,25 +2930,25 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F32" s="2">
         <v>232</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H32" s="2">
         <v>2</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J32" s="2">
         <v>0.001</v>
@@ -2939,25 +2962,25 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D33" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F33" s="2">
         <v>234</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H33" s="2">
         <v>2</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J33" s="2">
         <v>0.001</v>
@@ -2971,25 +2994,25 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="F34" s="2">
         <v>236</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H34" s="2">
         <v>2</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J34" s="2">
         <v>0.001</v>
@@ -3003,22 +3026,22 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F35" s="2">
         <v>238</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H35" s="2">
         <v>1</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J35" s="2">
         <v>1</v>
@@ -3032,22 +3055,22 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F36" s="2">
         <v>239</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H36" s="2">
         <v>1</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J36" s="2">
         <v>1</v>
@@ -3061,22 +3084,22 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F37" s="2">
         <v>240</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H37" s="2">
         <v>1</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J37" s="2">
         <v>1</v>
@@ -3090,22 +3113,22 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F38" s="2">
         <v>241</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H38" s="2">
         <v>1</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J38" s="2">
         <v>1</v>
@@ -3119,22 +3142,22 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F39" s="2">
         <v>242</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H39" s="2">
         <v>1</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J39" s="2">
         <v>1</v>
@@ -3148,22 +3171,22 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F40" s="2">
         <v>243</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H40" s="2">
         <v>1</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J40" s="2">
         <v>1</v>
@@ -3177,22 +3200,22 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F41" s="2">
         <v>244</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H41" s="2">
         <v>1</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J41" s="2">
         <v>1</v>
@@ -3206,22 +3229,22 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F42" s="2">
         <v>245</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H42" s="2">
         <v>1</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J42" s="2">
         <v>0.1</v>
@@ -3235,22 +3258,22 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F43" s="2">
         <v>246</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H43" s="2">
         <v>1</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J43" s="2">
         <v>1</v>
@@ -3264,25 +3287,25 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F44" s="2">
         <v>247</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H44" s="2">
         <v>1</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J44" s="2">
         <v>0.1</v>
@@ -3296,22 +3319,22 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F45" s="2">
         <v>248</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H45" s="2">
         <v>1</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J45" s="2">
         <v>1</v>
@@ -3325,22 +3348,22 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F46" s="2">
         <v>249</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H46" s="2">
         <v>1</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J46" s="2">
         <v>1</v>
@@ -3354,22 +3377,22 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F47" s="2">
         <v>250</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H47" s="2">
         <v>1</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J47" s="2">
         <v>1</v>
@@ -3383,22 +3406,22 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F48" s="2">
         <v>251</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H48" s="2">
         <v>1</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J48" s="2">
         <v>1</v>
@@ -3412,22 +3435,22 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F49" s="2">
         <v>252</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H49" s="2">
         <v>1</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J49" s="2">
         <v>1</v>
@@ -3441,22 +3464,22 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F50" s="2">
         <v>253</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H50" s="2">
         <v>1</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J50" s="2">
         <v>1</v>
@@ -3470,22 +3493,22 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F51" s="2">
         <v>254</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H51" s="2">
         <v>1</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J51" s="2">
         <v>1</v>
@@ -3499,22 +3522,22 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F52" s="2">
         <v>255</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H52" s="2">
         <v>1</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J52" s="2">
         <v>1</v>
@@ -3528,22 +3551,22 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F53" s="2">
         <v>256</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H53" s="2">
         <v>1</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J53" s="2">
         <v>1</v>
@@ -3557,22 +3580,22 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F54" s="2">
         <v>257</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H54" s="2">
         <v>1</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J54" s="2">
         <v>0.1</v>
@@ -3586,22 +3609,22 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F55" s="2">
         <v>258</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H55" s="2">
         <v>1</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J55" s="2">
         <v>1</v>
@@ -3615,22 +3638,22 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F56" s="2">
         <v>259</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H56" s="2">
         <v>1</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J56" s="2">
         <v>1</v>
@@ -3644,22 +3667,22 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F57" s="2">
         <v>260</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H57" s="2">
         <v>1</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J57" s="2">
         <v>1</v>
@@ -3673,22 +3696,22 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F58" s="2">
         <v>261</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H58" s="2">
         <v>1</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J58" s="2">
         <v>1</v>
@@ -3702,22 +3725,22 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F59" s="2">
         <v>262</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H59" s="2">
         <v>1</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J59" s="2">
         <v>1</v>
@@ -3731,25 +3754,25 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F60" s="2">
         <v>263</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H60" s="2">
         <v>1</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J60" s="2">
         <v>0.1</v>
@@ -3763,25 +3786,25 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F61" s="2">
         <v>264</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H61" s="2">
         <v>1</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J61" s="2">
         <v>0.1</v>
@@ -3795,25 +3818,25 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F62" s="2">
         <v>265</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H62" s="2">
         <v>1</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J62" s="2">
         <v>0.1</v>
@@ -3827,25 +3850,25 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F63" s="2">
         <v>266</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H63" s="2">
         <v>1</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J63" s="2">
         <v>0.1</v>
@@ -3859,25 +3882,25 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F64" s="2">
         <v>267</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H64" s="2">
         <v>1</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J64" s="2">
         <v>0.1</v>
@@ -3891,22 +3914,22 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F65" s="2">
         <v>268</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H65" s="2">
         <v>1</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J65" s="2">
         <v>0.1</v>
@@ -3920,22 +3943,22 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F66" s="3">
         <v>269</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H66" s="3">
         <v>1</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J66" s="3">
         <v>1</v>
@@ -3952,22 +3975,22 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F67" s="3">
         <v>270</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H67" s="3">
         <v>1</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J67" s="3">
         <v>1</v>
@@ -3984,22 +4007,22 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F68" s="2">
         <v>271</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H68" s="2">
         <v>1</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J68" s="2">
         <v>1</v>
@@ -4013,22 +4036,22 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F69" s="2">
         <v>272</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H69" s="2">
         <v>1</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J69" s="2">
         <v>1</v>
@@ -4042,22 +4065,22 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F70" s="2">
         <v>273</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H70" s="2">
         <v>1</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J70" s="2">
         <v>1</v>
@@ -4071,22 +4094,22 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F71" s="2">
         <v>274</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H71" s="2">
         <v>1</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J71" s="2">
         <v>1</v>
@@ -4100,22 +4123,22 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F72" s="2">
         <v>275</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H72" s="2">
         <v>1</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J72" s="2">
         <v>1</v>
@@ -4129,22 +4152,22 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F73" s="2">
         <v>276</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H73" s="2">
         <v>1</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J73" s="2">
         <v>1</v>
@@ -4158,22 +4181,22 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F74" s="2">
         <v>277</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H74" s="2">
         <v>1</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J74" s="2">
         <v>1</v>
@@ -4187,22 +4210,22 @@
         <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F75" s="2">
         <v>278</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H75" s="2">
         <v>1</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J75" s="2">
         <v>1</v>
@@ -4216,22 +4239,22 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F76" s="2">
         <v>279</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H76" s="2">
         <v>1</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J76" s="2">
         <v>1</v>
@@ -4245,22 +4268,22 @@
         <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F77" s="2">
         <v>280</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H77" s="2">
         <v>1</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J77" s="2">
         <v>1</v>
@@ -4274,25 +4297,25 @@
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F78" s="2">
         <v>281</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H78" s="2">
         <v>1</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J78" s="2">
         <v>0.1</v>
@@ -4306,25 +4329,25 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F79" s="2">
         <v>282</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H79" s="2">
         <v>1</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J79" s="2">
         <v>0.1</v>
@@ -4338,25 +4361,25 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F80" s="2">
         <v>283</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H80" s="2">
         <v>1</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J80" s="2">
         <v>0.1</v>
@@ -4370,25 +4393,25 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F81" s="2">
         <v>284</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H81" s="2">
         <v>1</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J81" s="2">
         <v>0.1</v>
@@ -4402,25 +4425,25 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F82" s="2">
         <v>285</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H82" s="2">
         <v>1</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J82" s="2">
         <v>0.1</v>
@@ -4434,25 +4457,25 @@
         <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F83" s="2">
         <v>286</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H83" s="2">
         <v>1</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J83" s="2">
         <v>0.1</v>
@@ -4466,25 +4489,25 @@
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F84" s="2">
         <v>287</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H84" s="2">
         <v>1</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J84" s="2">
         <v>0.1</v>
@@ -4498,25 +4521,25 @@
         <v>84</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F85" s="2">
         <v>288</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H85" s="2">
         <v>1</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J85" s="2">
         <v>0.1</v>
@@ -4530,25 +4553,25 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F86" s="2">
         <v>289</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H86" s="2">
         <v>1</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J86" s="2">
         <v>0.1</v>
@@ -4562,25 +4585,25 @@
         <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F87" s="2">
         <v>290</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H87" s="2">
         <v>1</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J87" s="2">
         <v>0.1</v>
@@ -4594,25 +4617,25 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F88" s="2">
         <v>291</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H88" s="2">
         <v>1</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J88" s="2">
         <v>0.1</v>
@@ -4626,25 +4649,25 @@
         <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F89" s="2">
         <v>292</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H89" s="2">
         <v>1</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J89" s="2">
         <v>0.1</v>
@@ -4658,25 +4681,25 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F90" s="2">
         <v>293</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H90" s="2">
         <v>1</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J90" s="2">
         <v>0.1</v>
@@ -4690,25 +4713,25 @@
         <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F91" s="2">
         <v>294</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H91" s="2">
         <v>1</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J91" s="2">
         <v>0.1</v>
@@ -4722,25 +4745,25 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F92" s="2">
         <v>295</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H92" s="2">
         <v>1</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J92" s="2">
         <v>0.1</v>
@@ -4754,22 +4777,22 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F93" s="3">
         <v>296</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H93" s="3">
         <v>1</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J93" s="3">
         <v>1</v>
@@ -4786,22 +4809,22 @@
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F94" s="3">
         <v>297</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H94" s="3">
         <v>1</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J94" s="3">
         <v>1</v>
@@ -4818,22 +4841,22 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F95" s="3">
         <v>298</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H95" s="3">
         <v>1</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J95" s="3">
         <v>1</v>
@@ -4850,22 +4873,22 @@
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F96" s="3">
         <v>299</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H96" s="3">
         <v>1</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J96" s="3">
         <v>1</v>
@@ -4882,22 +4905,22 @@
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F97" s="3">
         <v>300</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H97" s="3">
         <v>1</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J97" s="3">
         <v>1</v>
@@ -4914,22 +4937,22 @@
         <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F98" s="2">
         <v>501</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H98" s="2">
         <v>1</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J98" s="2">
         <v>1</v>
@@ -4943,22 +4966,22 @@
         <v>98</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F99" s="2">
         <v>502</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H99" s="2">
         <v>1</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J99" s="2">
         <v>1</v>
@@ -4972,22 +4995,22 @@
         <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F100" s="2">
         <v>503</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H100" s="2">
         <v>1</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J100" s="2">
         <v>1</v>
@@ -5001,22 +5024,22 @@
         <v>100</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F101" s="2">
         <v>504</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H101" s="2">
         <v>1</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J101" s="2">
         <v>1</v>
@@ -5030,22 +5053,22 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F102" s="2">
         <v>505</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H102" s="2">
         <v>1</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J102" s="2">
         <v>1</v>
@@ -5059,22 +5082,22 @@
         <v>102</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F103" s="2">
         <v>506</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H103" s="2">
         <v>1</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J103" s="2">
         <v>1</v>
@@ -5088,22 +5111,22 @@
         <v>103</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F104" s="2">
         <v>507</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H104" s="2">
         <v>1</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J104" s="2">
         <v>1</v>
@@ -5117,22 +5140,22 @@
         <v>104</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F105" s="2">
         <v>508</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H105" s="2">
         <v>1</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J105" s="2">
         <v>1</v>
@@ -5146,22 +5169,22 @@
         <v>105</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F106" s="2">
         <v>509</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H106" s="2">
         <v>1</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J106" s="2">
         <v>1</v>
@@ -5175,22 +5198,22 @@
         <v>106</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F107" s="2">
         <v>510</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H107" s="2">
         <v>1</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J107" s="2">
         <v>1</v>
@@ -5204,22 +5227,22 @@
         <v>107</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F108" s="2">
         <v>511</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H108" s="2">
         <v>1</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J108" s="2">
         <v>1</v>
@@ -5233,22 +5256,22 @@
         <v>108</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F109" s="2">
         <v>512</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H109" s="2">
         <v>1</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J109" s="2">
         <v>1</v>
@@ -5262,22 +5285,22 @@
         <v>109</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F110" s="2">
         <v>513</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H110" s="2">
         <v>1</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J110" s="2">
         <v>1</v>
@@ -5291,22 +5314,22 @@
         <v>110</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F111" s="2">
         <v>514</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H111" s="2">
         <v>1</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J111" s="2">
         <v>1</v>
@@ -5320,22 +5343,22 @@
         <v>111</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F112" s="2">
         <v>515</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H112" s="2">
         <v>1</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J112" s="2">
         <v>1</v>
@@ -5349,22 +5372,22 @@
         <v>112</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F113" s="2">
         <v>516</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H113" s="2">
         <v>1</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J113" s="2">
         <v>1</v>
@@ -5378,22 +5401,22 @@
         <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F114" s="2">
         <v>517</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H114" s="2">
         <v>1</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J114" s="2">
         <v>1</v>
@@ -5407,22 +5430,22 @@
         <v>114</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F115" s="2">
         <v>518</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H115" s="2">
         <v>1</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J115" s="2">
         <v>1</v>
@@ -5436,22 +5459,22 @@
         <v>115</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F116" s="2">
         <v>519</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H116" s="2">
         <v>1</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J116" s="2">
         <v>1</v>
@@ -5465,22 +5488,22 @@
         <v>116</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F117" s="2">
         <v>520</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H117" s="2">
         <v>1</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J117" s="2">
         <v>1</v>
@@ -5494,22 +5517,22 @@
         <v>117</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F118" s="2">
         <v>521</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H118" s="2">
         <v>1</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J118" s="2">
         <v>1</v>
@@ -5523,22 +5546,22 @@
         <v>118</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F119" s="2">
         <v>522</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H119" s="2">
         <v>1</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J119" s="2">
         <v>1</v>
@@ -5552,22 +5575,22 @@
         <v>119</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F120" s="2">
         <v>523</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H120" s="2">
         <v>1</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J120" s="2">
         <v>1</v>
@@ -5581,22 +5604,22 @@
         <v>120</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F121" s="2">
         <v>524</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H121" s="2">
         <v>1</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J121" s="2">
         <v>1</v>
@@ -5610,22 +5633,22 @@
         <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F122" s="2">
         <v>525</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H122" s="2">
         <v>1</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J122" s="2">
         <v>1</v>
@@ -5639,22 +5662,22 @@
         <v>122</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F123" s="2">
         <v>526</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H123" s="2">
         <v>1</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J123" s="2">
         <v>1</v>
@@ -5668,22 +5691,22 @@
         <v>123</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F124" s="2">
         <v>527</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H124" s="2">
         <v>1</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J124" s="2">
         <v>1</v>
@@ -5697,22 +5720,22 @@
         <v>124</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F125" s="2">
         <v>528</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H125" s="2">
         <v>1</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J125" s="2">
         <v>1</v>
@@ -5726,22 +5749,22 @@
         <v>125</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F126" s="2">
         <v>529</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H126" s="2">
         <v>1</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J126" s="2">
         <v>1</v>
@@ -5755,22 +5778,22 @@
         <v>126</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F127" s="2">
         <v>530</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H127" s="2">
         <v>1</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J127" s="2">
         <v>1</v>
@@ -5784,22 +5807,22 @@
         <v>127</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F128" s="2">
         <v>531</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H128" s="2">
         <v>1</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J128" s="2">
         <v>1</v>
@@ -5813,22 +5836,22 @@
         <v>128</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F129" s="2">
         <v>532</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H129" s="2">
         <v>1</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J129" s="2">
         <v>1</v>
@@ -5842,22 +5865,22 @@
         <v>129</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F130" s="2">
         <v>533</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H130" s="2">
         <v>1</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J130" s="2">
         <v>1</v>
@@ -5871,22 +5894,22 @@
         <v>130</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F131" s="2">
         <v>534</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H131" s="2">
         <v>1</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J131" s="2">
         <v>1</v>
@@ -5900,22 +5923,22 @@
         <v>131</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F132" s="2">
         <v>535</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H132" s="2">
         <v>1</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J132" s="2">
         <v>1</v>
@@ -5929,22 +5952,22 @@
         <v>132</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F133" s="2">
         <v>560</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H133" s="2">
         <v>1</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J133" s="2">
         <v>1</v>
@@ -5958,22 +5981,22 @@
         <v>133</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F134" s="2">
         <v>561</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H134" s="2">
         <v>1</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J134" s="2">
         <v>1</v>
@@ -5987,25 +6010,25 @@
         <v>134</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F135" s="2">
         <v>562</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H135" s="2">
         <v>1</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J135" s="2">
         <v>0.1</v>
@@ -6019,25 +6042,25 @@
         <v>135</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F136" s="2">
         <v>563</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H136" s="2">
         <v>1</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J136" s="2">
         <v>0.1</v>
@@ -6051,25 +6074,25 @@
         <v>136</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F137" s="2">
         <v>564</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H137" s="2">
         <v>1</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J137" s="2">
         <v>0.1</v>
@@ -6083,25 +6106,25 @@
         <v>137</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F138" s="2">
         <v>565</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H138" s="2">
         <v>1</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J138" s="2">
         <v>0.001</v>
@@ -6115,25 +6138,25 @@
         <v>138</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F139" s="2">
         <v>566</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H139" s="5">
         <v>1</v>
       </c>
       <c r="I139" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J139" s="5">
         <v>1</v>
@@ -6147,25 +6170,25 @@
         <v>139</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F140" s="2">
         <v>567</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H140" s="2">
         <v>1</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J140" s="2">
         <v>0.1</v>
@@ -6179,25 +6202,25 @@
         <v>140</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F141" s="2">
         <v>568</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H141" s="2">
         <v>1</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J141" s="2">
         <v>0.1</v>
@@ -6211,25 +6234,25 @@
         <v>141</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F142" s="2">
         <v>569</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H142" s="2">
         <v>1</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J142" s="2">
         <v>0.1</v>
@@ -6243,25 +6266,25 @@
         <v>142</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F143" s="2">
         <v>570</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H143" s="2">
         <v>1</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J143" s="2">
         <v>0.1</v>
@@ -6275,25 +6298,25 @@
         <v>143</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F144" s="2">
         <v>571</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H144" s="2">
         <v>1</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J144" s="2">
         <v>0.1</v>
@@ -6307,25 +6330,25 @@
         <v>144</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F145" s="2">
         <v>572</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H145" s="2">
         <v>1</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J145" s="2">
         <v>0.1</v>
@@ -6339,25 +6362,25 @@
         <v>145</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F146" s="2">
         <v>573</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H146" s="2">
         <v>1</v>
       </c>
       <c r="I146" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J146" s="2">
         <v>0.1</v>
@@ -6371,25 +6394,25 @@
         <v>146</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F147" s="2">
         <v>574</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H147" s="2">
         <v>1</v>
       </c>
       <c r="I147" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J147" s="2">
         <v>0.1</v>
@@ -6403,22 +6426,22 @@
         <v>147</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F148" s="2">
         <v>600</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H148" s="2">
         <v>1</v>
       </c>
       <c r="I148" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J148" s="2">
         <v>0.01</v>
@@ -6432,22 +6455,22 @@
         <v>148</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F149" s="2">
         <v>601</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H149" s="2">
         <v>1</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J149" s="2">
         <v>0.01</v>
@@ -6461,22 +6484,22 @@
         <v>149</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F150" s="2">
         <v>602</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H150" s="2">
         <v>1</v>
       </c>
       <c r="I150" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J150" s="2">
         <v>0.01</v>
@@ -6490,22 +6513,22 @@
         <v>150</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F151" s="2">
         <v>603</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H151" s="2">
         <v>1</v>
       </c>
       <c r="I151" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J151" s="2">
         <v>0.01</v>
@@ -6519,22 +6542,22 @@
         <v>151</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F152" s="2">
         <v>604</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H152" s="2">
         <v>1</v>
       </c>
       <c r="I152" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J152" s="2">
         <v>0.01</v>
@@ -6548,22 +6571,22 @@
         <v>152</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F153" s="2">
         <v>605</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H153" s="2">
         <v>1</v>
       </c>
       <c r="I153" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J153" s="2">
         <v>0.01</v>
@@ -6577,22 +6600,22 @@
         <v>153</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F154" s="2">
         <v>606</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H154" s="2">
         <v>1</v>
       </c>
       <c r="I154" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J154" s="2">
         <v>0.01</v>
@@ -6606,22 +6629,22 @@
         <v>154</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F155" s="2">
         <v>607</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H155" s="2">
         <v>1</v>
       </c>
       <c r="I155" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J155" s="2">
         <v>0.01</v>
@@ -6635,22 +6658,22 @@
         <v>155</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F156" s="2">
         <v>608</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H156" s="2">
         <v>1</v>
       </c>
       <c r="I156" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J156" s="2">
         <v>0.01</v>
@@ -6664,22 +6687,22 @@
         <v>156</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F157" s="2">
         <v>609</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H157" s="2">
         <v>1</v>
       </c>
       <c r="I157" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J157" s="2">
         <v>1</v>
@@ -6693,22 +6716,22 @@
         <v>157</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F158" s="2">
         <v>610</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H158" s="2">
         <v>1</v>
       </c>
       <c r="I158" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J158" s="2">
         <v>1</v>
@@ -6722,22 +6745,22 @@
         <v>158</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F159" s="2">
         <v>611</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H159" s="5">
         <v>1</v>
       </c>
       <c r="I159" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J159" s="5">
         <v>1</v>
@@ -6751,22 +6774,22 @@
         <v>159</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F160" s="2">
         <v>612</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H160" s="5">
         <v>1</v>
       </c>
       <c r="I160" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J160" s="5">
         <v>1</v>
@@ -6780,22 +6803,22 @@
         <v>160</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F161" s="2">
         <v>613</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H161" s="5">
         <v>1</v>
       </c>
       <c r="I161" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J161" s="5">
         <v>1</v>
@@ -6809,27 +6832,27 @@
         <v>161</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F162" s="3">
         <v>614</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H162" s="7">
-        <v>1</v>
-      </c>
-      <c r="I162" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J162" s="7">
-        <v>1</v>
-      </c>
-      <c r="K162" s="7">
+        <v>19</v>
+      </c>
+      <c r="H162" s="6">
+        <v>1</v>
+      </c>
+      <c r="I162" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J162" s="6">
+        <v>1</v>
+      </c>
+      <c r="K162" s="6">
         <v>0</v>
       </c>
       <c r="L162" s="6">
@@ -6841,27 +6864,27 @@
         <v>162</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F163" s="3">
         <v>615</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H163" s="7">
-        <v>1</v>
-      </c>
-      <c r="I163" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J163" s="7">
-        <v>1</v>
-      </c>
-      <c r="K163" s="7">
+        <v>19</v>
+      </c>
+      <c r="H163" s="6">
+        <v>1</v>
+      </c>
+      <c r="I163" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J163" s="6">
+        <v>1</v>
+      </c>
+      <c r="K163" s="6">
         <v>0</v>
       </c>
       <c r="L163" s="6">
@@ -6873,27 +6896,27 @@
         <v>163</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F164" s="3">
         <v>616</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H164" s="7">
-        <v>1</v>
-      </c>
-      <c r="I164" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J164" s="7">
-        <v>1</v>
-      </c>
-      <c r="K164" s="7">
+        <v>19</v>
+      </c>
+      <c r="H164" s="6">
+        <v>1</v>
+      </c>
+      <c r="I164" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J164" s="6">
+        <v>1</v>
+      </c>
+      <c r="K164" s="6">
         <v>0</v>
       </c>
       <c r="L164" s="6">
@@ -6905,22 +6928,22 @@
         <v>164</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F165" s="2">
         <v>617</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H165" s="5">
         <v>1</v>
       </c>
       <c r="I165" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J165" s="5">
         <v>1</v>
@@ -6934,22 +6957,22 @@
         <v>165</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F166" s="2">
         <v>618</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H166" s="5">
         <v>1</v>
       </c>
       <c r="I166" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J166" s="5">
         <v>1</v>
@@ -6963,22 +6986,22 @@
         <v>166</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F167" s="2">
         <v>619</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H167" s="5">
         <v>1</v>
       </c>
       <c r="I167" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J167" s="5">
         <v>1</v>
@@ -6992,22 +7015,22 @@
         <v>167</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F168" s="2">
         <v>620</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H168" s="5">
         <v>1</v>
       </c>
       <c r="I168" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J168" s="5">
         <v>1</v>
@@ -7021,22 +7044,22 @@
         <v>168</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F169" s="2">
         <v>621</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H169" s="5">
         <v>1</v>
       </c>
       <c r="I169" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J169" s="5">
         <v>1</v>
@@ -7050,22 +7073,22 @@
         <v>169</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F170" s="2">
         <v>622</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H170" s="5">
         <v>1</v>
       </c>
       <c r="I170" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J170" s="5">
         <v>1</v>
@@ -7079,22 +7102,22 @@
         <v>170</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F171" s="2">
         <v>623</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H171" s="5">
         <v>1</v>
       </c>
       <c r="I171" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J171" s="5">
         <v>1</v>
@@ -7108,22 +7131,22 @@
         <v>171</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F172" s="2">
         <v>624</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H172" s="5">
         <v>1</v>
       </c>
       <c r="I172" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J172" s="5">
         <v>1</v>
@@ -7137,22 +7160,22 @@
         <v>172</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F173" s="2">
         <v>625</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H173" s="5">
         <v>1</v>
       </c>
       <c r="I173" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J173" s="5">
         <v>1</v>
@@ -7166,22 +7189,22 @@
         <v>173</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F174" s="2">
         <v>626</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H174" s="5">
         <v>1</v>
       </c>
       <c r="I174" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J174" s="5">
         <v>1</v>
@@ -7195,27 +7218,27 @@
         <v>174</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F175" s="3">
         <v>627</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H175" s="7">
-        <v>1</v>
-      </c>
-      <c r="I175" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J175" s="7">
-        <v>1</v>
-      </c>
-      <c r="K175" s="7">
+        <v>19</v>
+      </c>
+      <c r="H175" s="6">
+        <v>1</v>
+      </c>
+      <c r="I175" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J175" s="6">
+        <v>1</v>
+      </c>
+      <c r="K175" s="6">
         <v>0</v>
       </c>
       <c r="L175" s="6">
@@ -7227,27 +7250,27 @@
         <v>175</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F176" s="3">
         <v>628</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H176" s="7">
-        <v>1</v>
-      </c>
-      <c r="I176" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J176" s="7">
-        <v>1</v>
-      </c>
-      <c r="K176" s="7">
+        <v>19</v>
+      </c>
+      <c r="H176" s="6">
+        <v>1</v>
+      </c>
+      <c r="I176" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J176" s="6">
+        <v>1</v>
+      </c>
+      <c r="K176" s="6">
         <v>0</v>
       </c>
       <c r="L176" s="6">
@@ -7259,22 +7282,22 @@
         <v>176</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F177" s="2">
         <v>629</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H177" s="5">
         <v>1</v>
       </c>
       <c r="I177" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J177" s="5">
         <v>1</v>
@@ -7288,22 +7311,22 @@
         <v>177</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F178" s="2">
         <v>630</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H178" s="5">
         <v>1</v>
       </c>
       <c r="I178" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J178" s="5">
         <v>1</v>
@@ -7317,22 +7340,22 @@
         <v>178</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F179" s="2">
         <v>631</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H179" s="5">
         <v>1</v>
       </c>
       <c r="I179" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J179" s="5">
         <v>1</v>
@@ -7346,22 +7369,22 @@
         <v>179</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F180" s="2">
         <v>632</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H180" s="5">
         <v>1</v>
       </c>
       <c r="I180" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J180" s="5">
         <v>1</v>
@@ -7434,22 +7457,22 @@
         <v>1000</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F2" s="2">
         <v>81</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H2" s="2">
         <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J2" s="2">
         <v>1</v>
@@ -7463,22 +7486,22 @@
         <v>1001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F3" s="2">
         <v>82</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H3" s="2">
         <v>1</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J3" s="2">
         <v>1</v>
@@ -7492,22 +7515,22 @@
         <v>1002</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F4" s="2">
         <v>83</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H4" s="2">
         <v>1</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J4" s="2">
         <v>1</v>
@@ -7521,22 +7544,22 @@
         <v>1003</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="F5" s="2">
         <v>84</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H5" s="2">
         <v>1</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J5" s="2">
         <v>1</v>
@@ -7550,22 +7573,22 @@
         <v>1004</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F6" s="2">
         <v>85</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J6" s="2">
         <v>1</v>
@@ -7579,22 +7602,22 @@
         <v>1005</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F7" s="2">
         <v>86</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J7" s="2">
         <v>1</v>
@@ -7608,22 +7631,22 @@
         <v>1006</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F8" s="2">
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J8" s="2">
         <v>1</v>
@@ -7637,22 +7660,22 @@
         <v>1007</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F9" s="2">
         <v>88</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J9" s="2">
         <v>1</v>
@@ -7666,22 +7689,22 @@
         <v>1008</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F10" s="2">
         <v>89</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J10" s="2">
         <v>1</v>
@@ -7695,22 +7718,22 @@
         <v>1009</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F11" s="2">
         <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J11" s="2">
         <v>1</v>
@@ -7723,23 +7746,23 @@
       <c r="A12" s="3">
         <v>1010</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>90</v>
+      <c r="B12" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F12" s="3">
         <v>91</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H12" s="3">
         <v>1</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J12" s="3">
         <v>1</v>
@@ -7755,23 +7778,23 @@
       <c r="A13" s="3">
         <v>1011</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>90</v>
+      <c r="B13" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F13" s="3">
         <v>92</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H13" s="3">
         <v>1</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J13" s="3">
         <v>1</v>
@@ -7787,23 +7810,23 @@
       <c r="A14" s="3">
         <v>1012</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>90</v>
+      <c r="B14" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F14" s="3">
         <v>93</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H14" s="3">
         <v>1</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J14" s="3">
         <v>1</v>
@@ -7820,22 +7843,22 @@
         <v>1013</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F15" s="2">
         <v>94</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J15" s="2">
         <v>1</v>
@@ -7849,22 +7872,22 @@
         <v>1014</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F16" s="2">
         <v>95</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J16" s="2">
         <v>1</v>
@@ -7878,22 +7901,22 @@
         <v>1015</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F17" s="2">
         <v>96</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J17" s="2">
         <v>1</v>
@@ -7967,25 +7990,25 @@
         <v>2000</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F2" s="2">
         <v>301</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H2" s="2">
         <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J2" s="2">
         <v>1</v>
@@ -7999,25 +8022,25 @@
         <v>2001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F3" s="2">
         <v>302</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H3" s="2">
         <v>1</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J3" s="2">
         <v>0.1</v>
@@ -8031,25 +8054,25 @@
         <v>2002</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F4" s="2">
         <v>303</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H4" s="2">
         <v>1</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J4" s="2">
         <v>0.1</v>
@@ -8063,25 +8086,25 @@
         <v>2003</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F5" s="2">
         <v>304</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H5" s="2">
         <v>1</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J5" s="2">
         <v>0.1</v>
@@ -8095,25 +8118,25 @@
         <v>2004</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F6" s="2">
         <v>305</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J6" s="2">
         <v>0.1</v>
@@ -8127,22 +8150,22 @@
         <v>2005</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F7" s="2">
         <v>306</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J7" s="2">
         <v>1</v>
@@ -8156,25 +8179,25 @@
         <v>2006</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F8" s="2">
         <v>307</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J8" s="2">
         <v>1</v>
@@ -8188,25 +8211,25 @@
         <v>2007</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F9" s="2">
         <v>308</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J9" s="2">
         <v>0.01</v>
@@ -8220,25 +8243,25 @@
         <v>2008</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F10" s="2">
         <v>309</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J10" s="2">
         <v>0.1</v>
@@ -8252,25 +8275,25 @@
         <v>2009</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F11" s="2">
         <v>310</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J11" s="2">
         <v>0.1</v>
@@ -8284,25 +8307,25 @@
         <v>2010</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F12" s="2">
         <v>311</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J12" s="2">
         <v>0.1</v>
@@ -8316,25 +8339,25 @@
         <v>2011</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F13" s="2">
         <v>312</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J13" s="2">
         <v>0.1</v>
@@ -8348,25 +8371,25 @@
         <v>2012</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F14" s="2">
         <v>313</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J14" s="2">
         <v>0.1</v>
@@ -8380,25 +8403,25 @@
         <v>2013</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F15" s="2">
         <v>314</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J15" s="2">
         <v>0.1</v>
@@ -8412,25 +8435,25 @@
         <v>2014</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F16" s="2">
         <v>315</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J16" s="2">
         <v>1</v>
@@ -8444,25 +8467,25 @@
         <v>2015</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F17" s="2">
         <v>316</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J17" s="2">
         <v>1</v>
@@ -8476,25 +8499,25 @@
         <v>2016</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F18" s="2">
         <v>317</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J18" s="2">
         <v>1</v>
@@ -8508,22 +8531,22 @@
         <v>2017</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F19" s="3">
         <v>318</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H19" s="3">
         <v>1</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J19" s="3">
         <v>1</v>
@@ -8540,25 +8563,25 @@
         <v>2018</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F20" s="2">
         <v>319</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J20" s="2">
         <v>0.01</v>
@@ -8572,22 +8595,22 @@
         <v>2019</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F21" s="2">
         <v>320</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J21" s="2">
         <v>0.1</v>
@@ -8601,22 +8624,22 @@
         <v>2020</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F22" s="2">
         <v>321</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J22" s="2">
         <v>1</v>
@@ -8630,22 +8653,22 @@
         <v>2021</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>13</v>
+        <v>94</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="F23" s="3">
         <v>322</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H23" s="3">
         <v>1</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J23" s="3">
         <v>1</v>
@@ -8662,22 +8685,22 @@
         <v>2022</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F24" s="2">
         <v>323</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J24" s="2">
         <v>1</v>
@@ -8691,22 +8714,22 @@
         <v>2023</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F25" s="2">
         <v>324</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J25" s="2">
         <v>1</v>
@@ -8720,25 +8743,25 @@
         <v>2024</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F26" s="2">
         <v>325</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J26" s="2">
         <v>1</v>
@@ -8752,25 +8775,25 @@
         <v>2025</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F27" s="2">
         <v>326</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J27" s="2">
         <v>1</v>
@@ -8784,25 +8807,25 @@
         <v>2026</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F28" s="2">
         <v>327</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J28" s="2">
         <v>1</v>
@@ -8816,25 +8839,25 @@
         <v>2027</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F29" s="2">
         <v>328</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J29" s="2">
         <v>1</v>
@@ -8848,22 +8871,22 @@
         <v>2028</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F30" s="2">
         <v>329</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J30" s="2">
         <v>1</v>
@@ -8877,22 +8900,22 @@
         <v>2029</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F31" s="2">
         <v>330</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J31" s="2">
         <v>1</v>
@@ -8906,22 +8929,22 @@
         <v>2030</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F32" s="2">
         <v>331</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H32" s="2">
         <v>1</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J32" s="2">
         <v>1</v>
@@ -8935,22 +8958,22 @@
         <v>2031</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F33" s="2">
         <v>332</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H33" s="2">
         <v>1</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J33" s="2">
         <v>1</v>
@@ -8964,22 +8987,22 @@
         <v>2032</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F34" s="2">
         <v>333</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J34" s="2">
         <v>1</v>
@@ -8993,22 +9016,22 @@
         <v>2033</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F35" s="2">
         <v>334</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H35" s="2">
         <v>1</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J35" s="2">
         <v>1</v>
@@ -9022,22 +9045,22 @@
         <v>2034</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F36" s="2">
         <v>335</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H36" s="2">
         <v>1</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J36" s="2">
         <v>1</v>
@@ -9051,22 +9074,22 @@
         <v>2035</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F37" s="2">
         <v>336</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H37" s="2">
         <v>1</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J37" s="2">
         <v>0.001</v>
@@ -9080,22 +9103,22 @@
         <v>2036</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>20</v>
+        <v>94</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="F38" s="3">
         <v>337</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H38" s="3">
         <v>1</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J38" s="3">
         <v>1</v>
@@ -9112,22 +9135,22 @@
         <v>2037</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>20</v>
+        <v>94</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="F39" s="3">
         <v>338</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H39" s="3">
         <v>1</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J39" s="3">
         <v>1</v>
@@ -9144,22 +9167,22 @@
         <v>2038</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>20</v>
+        <v>94</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="F40" s="3">
         <v>339</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H40" s="3">
         <v>1</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J40" s="3">
         <v>1</v>
@@ -9176,22 +9199,22 @@
         <v>2039</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F41" s="2">
         <v>340</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H41" s="2">
         <v>1</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J41" s="2">
         <v>1</v>
@@ -9205,25 +9228,25 @@
         <v>2040</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F42" s="2">
         <v>341</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H42" s="2">
         <v>1</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J42" s="2">
         <v>0.001</v>
@@ -9237,25 +9260,25 @@
         <v>2041</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F43" s="2">
         <v>342</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H43" s="2">
         <v>1</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J43" s="2">
         <v>1</v>
@@ -9269,22 +9292,22 @@
         <v>2042</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F44" s="2">
         <v>343</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H44" s="2">
         <v>1</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J44" s="2">
         <v>1</v>
@@ -9357,22 +9380,22 @@
         <v>3000</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H2" s="2">
         <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J2" s="2">
         <v>1</v>
@@ -9386,22 +9409,22 @@
         <v>3001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F3" s="2">
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H3" s="2">
         <v>1</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J3" s="2">
         <v>1</v>
@@ -9415,22 +9438,22 @@
         <v>3002</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F4" s="2">
         <v>3</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H4" s="2">
         <v>1</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J4" s="2">
         <v>1</v>
@@ -9444,22 +9467,22 @@
         <v>3003</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F5" s="2">
         <v>4</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H5" s="2">
         <v>1</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J5" s="2">
         <v>1</v>
@@ -9473,22 +9496,22 @@
         <v>3004</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F6" s="2">
         <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J6" s="2">
         <v>1</v>
@@ -9502,22 +9525,22 @@
         <v>3005</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F7" s="2">
         <v>6</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J7" s="2">
         <v>1</v>
@@ -9531,22 +9554,22 @@
         <v>3006</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F8" s="2">
         <v>7</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J8" s="2">
         <v>1</v>
@@ -9560,22 +9583,22 @@
         <v>3007</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F9" s="2">
         <v>8</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J9" s="2">
         <v>1</v>
@@ -9589,22 +9612,22 @@
         <v>3008</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F10" s="3">
         <v>9</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H10" s="3">
         <v>1</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J10" s="3">
         <v>1</v>
@@ -9621,22 +9644,22 @@
         <v>3009</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F11" s="3">
         <v>10</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H11" s="3">
         <v>1</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J11" s="3">
         <v>1</v>
@@ -9653,22 +9676,22 @@
         <v>3010</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F12" s="3">
         <v>11</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H12" s="3">
         <v>1</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J12" s="3">
         <v>1</v>
@@ -9685,22 +9708,22 @@
         <v>3011</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F13" s="3">
         <v>12</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H13" s="3">
         <v>1</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J13" s="3">
         <v>1</v>
@@ -9717,22 +9740,22 @@
         <v>3012</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F14" s="3">
         <v>13</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H14" s="3">
         <v>1</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J14" s="3">
         <v>1</v>
@@ -9749,22 +9772,22 @@
         <v>3013</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F15" s="3">
         <v>14</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H15" s="3">
         <v>1</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J15" s="3">
         <v>1</v>
@@ -9781,22 +9804,22 @@
         <v>3014</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F16" s="3">
         <v>15</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H16" s="3">
         <v>1</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J16" s="3">
         <v>1</v>
@@ -9813,22 +9836,22 @@
         <v>3015</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F17" s="3">
         <v>16</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H17" s="3">
         <v>1</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J17" s="3">
         <v>1</v>

--- a/config/PCS_125_英博.xlsx
+++ b/config/PCS_125_英博.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2679" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2680" uniqueCount="634">
   <si>
     <t>序号</t>
   </si>
@@ -377,6 +377,13 @@
     <t>{"en":"PCS operating status"}</t>
   </si>
   <si>
+    <t>0 停机|stop
+1 自检|self-check
+2 运行|running
+4 故障|fault
+7 待机|standby</t>
+  </si>
+  <si>
     <t>PCS 交流累计充电电量</t>
   </si>
   <si>
@@ -1199,6 +1206,24 @@
     <t>{"en":"PCS control software fault word 1"}</t>
   </si>
   <si>
+    <t>硬件故障-A 相硬件过流|Hardware fault - Phase A hardware overcurrent|2
+硬件故障-B 相硬件过流|Hardware fault - Phase B hardware overcurrent|2
+硬件故障-C 相硬件过流|Hardware fault - Phase C hardware overcurrent|2
+硬件故障-N 相硬件过流|Hardware fault - Phase N hardware overcurrent|2
+硬件故障-交流直流功率不匹配|Hardware fault - AC/DC power mismatch|2
+硬件故障-辅助源掉电|Hardware fault - Auxiliary source power failure|2
+硬件故障-温度过低或传感器故障|Hardware fault - Low temperature or sensor failure|2
+硬件故障-保留|Hardware fault - Reserved|0
+硬件故障-绝缘故障|Hardware fault - Insulation failure|2
+硬件故障-总驱动故障|Hardware fault - Total drive failure|2
+软件故障-A 相驱动故障|Software fault - Phase A drive failure|2
+硬件故障-B 相驱动故障|Hardware fault - Phase B drive failure|2
+硬件故障-C 相驱动故障|Hardware fault - Phase C drive failure|2
+硬件故障-N 相驱动故障|Hardware fault - Phase N drive failure|2
+硬件故障-散热器过温故障|Hardware fault - Heatsink overtemperature fault|2
+硬件故障-环境过温故障|Hardware fault - Environmental overtemperature fault|2</t>
+  </si>
+  <si>
     <t>PCS 控制软件故障字 2</t>
   </si>
   <si>
@@ -1208,6 +1233,24 @@
     <t>{"en":"PCS control software fault word 2"}</t>
   </si>
   <si>
+    <t>软件故障-A 相输出过载|Software fault - Phase A output overload|2
+软件故障-A 相输出过流|Software fault - Phase A output overcurrent|2
+软件故障-B 相输出过载|Software fault - Phase B output overload|2
+软件故障-B 相输出过流|Software fault - Phase B output overcurrent|2
+软件故障-C 相输出过载|Software fault - Phase C output overload|2
+软件故障-C 相输出过流|Software fault - Phase C output overcurrent|2
+软件故障-N 相输出过载|Software fault - Phase N output overload|2
+软件故障-N 相输出过流|Software fault - Phase N output overcurrent|2
+软件故障-交流过压|Software fault - AC overvoltage|2
+软件故障-交流欠压|Software fault - AC undervoltage|2
+软件故障-交流输出过压|Software fault - AC output overvoltage|2
+软件故障-交流输出欠压|Software fault - AC output undervoltage|2
+软件故障-THDU 超限|Software fault - THDU over limit|2
+软件故障-交流缺相|Software fault - AC phase loss|2
+软件故障-交流相序错误|Software fault - AC phase sequence error|2
+软件故障-直流反接故障|Software fault - DC reverse connection fault|2</t>
+  </si>
+  <si>
     <t>PCS 控制软件故障字 3</t>
   </si>
   <si>
@@ -1217,6 +1260,24 @@
     <t>{"en":"PCS control software fault word 3"}</t>
   </si>
   <si>
+    <t>软件故障-直流母线软件过压|Software fault - DC bus software overvoltage|2
+软件故障-直流母线软件欠压|Software fault - DC bus software undervoltage|2
+软件故障-交流过频|Software fault - AC overfrequency|2
+软件故障-交流欠频|Software fault - AC underfrequency|2
+软件故障-直流充电过流|Software fault - DC charging overcurrent|2
+软件故障-直流放电过流|Software fault - DC discharging overcurrent|2
+软件故障-SPI 通信故障|Software fault - SPI communication fault|2
+软件故障-直流分量超标|Software fault - DC component over limit|2
+软件故障-交流继电器合闸故障|Software fault - AC relay closing fault|2
+软件故障-交流继电器分闸故障|Software fault - AC relay opening fault|2
+软件故障-交流软启继电器合闸故障|Software fault - AC soft-start relay closing fault|2
+软件故障-交流软启继电器分闸故障|Software fault - AC soft-start relay opening fault|2
+软件故障-直流主正合闸故障|Software fault - DC main positive closing fault|2
+软件故障-直流主正分闸故障|Software fault - DC main positive opening fault|2
+软件故障-直流主负合闸故障|Software fault - DC main negative closing fault|2
+软件故障-直流主负分闸故障|Software fault - DC main negative opening fault|2</t>
+  </si>
+  <si>
     <t>PCS 控制软件故障字 4</t>
   </si>
   <si>
@@ -1226,6 +1287,24 @@
     <t>{"en":"PCS control software fault word 4"}</t>
   </si>
   <si>
+    <t>软件故障-铁电参数保存错误|Software fault - Ferroelectric parameter save error|2
+软件故障-直流软起失败|Software fault - DC soft start failure|2
+软件故障-交直流电压不匹配|Software fault - AC/DC voltage mismatch|2
+软件故障-电网孤岛故障|Software fault - Grid islanding fault|2
+软件故障-启动条件不满足|Software fault - Start condition not met|2
+软件故障-运行中开关故障|Software fault - Switch fault during operation|2
+软件故障-启动超时故障|Software fault - Start timeout fault|2
+软件故障-参数配置设置错误|Software fault - Parameter configuration error|2
+软件故障-支路瞬时值不平衡故障|Software fault - Branch instantaneous value imbalance fault|2
+软件故障-直路有效值不平衡异常|Software fault - DC RMS value imbalance anomaly|2
+软件故障-交流电压不平衡故障|Software fault - AC voltage imbalance fault|2
+软件告警-参数升级故障|Software warning - Parameter upgrade fault|1
+软件故障-保留|Software fault - Reserved|0
+软件故障-铁电芯片故障|Software fault - Ferroelectric chip fault|2
+硬件故障-保险熔断故障|Hardware fault - Fuse blown fault|2
+软件故障-光纤通讯故障|Software fault - Fiber optic communication fault|2</t>
+  </si>
+  <si>
     <t>PCS 控制软件故障字 5</t>
   </si>
   <si>
@@ -1235,6 +1314,24 @@
     <t>{"en":"PCS control software fault word 5"}</t>
   </si>
   <si>
+    <t>软件故障-保留|Software fault - Reserved|0
+软件故障-电池软件过压|Software fault - Battery software overvoltage|2
+软件故障-电池软件欠压|Software fault - Battery software undervoltage|2
+软件故障-母线电压不平衡|Software fault - Bus voltage imbalance|2
+软件故障-半母线过压|Software fault - Half bus overvoltage|2
+软件故障-保留|Software fault - Reserved|0
+软件故障-内部通信掉线|Software fault - Internal communication disconnection|2
+漏电流超限保护|Leakage current over limit protection|2
+硬件故障-零漂|Hardware fault - Zero drift|2
+硬件故障-直流软起故障|Hardware fault - DC soft start fault|2
+硬件故障-交流过流|Hardware fault - AC overcurrent|2
+软件故障-交流过流|Software fault - AC overcurrent|2
+硬件故障-半母线过压|Hardware fault - Half bus overvoltage|2
+硬件故障-直流过压|Hardware fault - DC overvoltage|2
+硬件故障-交流软起故障|Hardware fault - AC soft start fault|2
+软件故障-保留|Software fault - Reserved|0</t>
+  </si>
+  <si>
     <t>PCS 通讯软件故障字 1</t>
   </si>
   <si>
@@ -1244,6 +1341,24 @@
     <t>{"en":"PCS communication software fault word 1"}</t>
   </si>
   <si>
+    <t>软件故障-ARM_内部通讯故障|Software fault - ARM internal communication fault|2
+软件故障-ARM_EMS 通讯故障|Software fault - ARM EMS communication fault|2
+软件故障-ARM_SPI 故障录波通讯故障|Software fault - ARM SPI fault recording communication fault|2
+软件故障-ARM_SD 卡故障|Software fault - ARM SD card fault|2
+软件故障-ARM_RTC 故障|Software fault - ARM RTC fault|2
+软件故障-ARM_内部通讯协议版本不匹配|Software fault - ARM internal communication protocol version mismatch|2
+软件故障-ARM_COM1 网口通讯故障|Software fault - ARM COM1 network port communication fault|2
+软件故障-保留|Software fault - Reserved|0
+软件故障-ARM_急停输入信号反馈|Software fault - ARM emergency stop input signal feedback|2
+软件故障-ARM_BMS 干节点信号反馈|Software fault - ARM BMS dry contact signal feedback|2
+软件故障-ARM_英博 STS 开关晶闸管过温|Software fault - ARM Yingbo STS switch thyristor overtemperature|2
+软件故障-保留|Software fault - Reserved|0
+软件故障-保留|Software fault - Reserved|0
+软件故障-保留|Software fault - Reserved|0
+软件故障-保留|Software fault - Reserved|0
+软件故障-保留|Software fault - Reserved|0</t>
+  </si>
+  <si>
     <t>PCS 通讯软件故障字 2</t>
   </si>
   <si>
@@ -1253,6 +1368,24 @@
     <t>{"en":"PCS communication software fault word 2"}</t>
   </si>
   <si>
+    <t>软件故障-ARM_BMS 通讯故障|Software fault - ARM BMS communication fault|2
+软件故障-ARM_BMS 温度异常|Software fault - ARM BMS temperature abnormal|2
+软件故障-ARM_BMS 跳机|Software fault - ARM BMS trip|2
+软件故障-ARM_BMS 电池告警|Software fault - ARM BMS battery warning|1
+软件故障-保留|Software fault - Reserved|0
+软件故障-保留|Software fault - Reserved|0
+软件故障-ARM_软件急停故障反馈|Software fault - ARM software emergency stop fault feedback|2
+软件故障-保留|Software fault - Reserved|0
+软件故障-保留|Software fault - Reserved|0
+软件故障-保留|Software fault - Reserved|0
+软件故障-保留|Software fault - Reserved|0
+软件故障-保留|Software fault - Reserved|0
+软件故障-保留|Software fault - Reserved|0
+软件故障-保留|Software fault - Reserved|0
+软件故障-保留|Software fault - Reserved|0
+软件故障-保留|Software fault - Reserved|0</t>
+  </si>
+  <si>
     <t>PCS 通讯软件故障字 3</t>
   </si>
   <si>
@@ -1487,13 +1620,6 @@
     <t>运行模式选择</t>
   </si>
   <si>
-    <t>0 无
-1 恒流充电
-2 恒压充电
-3 恒功率充电
-4 直流恒压模式</t>
-  </si>
-  <si>
     <t>HoldingRegisters</t>
   </si>
   <si>
@@ -1503,6 +1629,13 @@
     <t>{"en":"Operation mode selection"}</t>
   </si>
   <si>
+    <t>0 无|None
+1 恒流充电|Constant current charging
+2 恒压充电|Constant voltage charging
+3 恒功率充电|Constant power charging
+4 直流恒压模式|DC constant voltage mode</t>
+  </si>
+  <si>
     <t>恒压充电电压设定值</t>
   </si>
   <si>
@@ -1546,6 +1679,11 @@
   </si>
   <si>
     <t>{"en":"Off grid setting"}</t>
+  </si>
+  <si>
+    <t>0 并网模式|Grid-connected mode
+1 VF离网模式|VF off-grid mode
+2 VSG模式|VSG mode</t>
   </si>
   <si>
     <t>离网输出电压给定（三相三线制）</t>
@@ -2550,7 +2688,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2565,13 +2703,25 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2926,15 +3076,17 @@
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="9.11111111111111" style="2"/>
-    <col min="2" max="2" width="22.8376068376068" style="2" customWidth="1"/>
+    <col min="2" max="2" width="22.8412698412698" style="2" customWidth="1"/>
     <col min="3" max="5" width="9.11111111111111" style="2"/>
-    <col min="6" max="6" width="10.957264957265" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.3931623931624" style="2" customWidth="1"/>
-    <col min="8" max="9" width="11.7435897435897" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.9603174603175" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.3968253968254" style="2" customWidth="1"/>
+    <col min="8" max="9" width="11.7460317460317" style="2" customWidth="1"/>
     <col min="10" max="12" width="9.11111111111111" style="2"/>
-    <col min="13" max="13" width="50.0512820512821" style="2" customWidth="1"/>
-    <col min="14" max="14" width="60.6153846153846" style="2" customWidth="1"/>
-    <col min="15" max="32" width="9.11111111111111" style="2"/>
+    <col min="13" max="13" width="50.0476190476191" style="2" customWidth="1"/>
+    <col min="14" max="14" width="60.6190476190476" style="2" customWidth="1"/>
+    <col min="15" max="15" width="23.8015873015873" style="2" customWidth="1"/>
+    <col min="16" max="16" width="78.6428571428571" style="5" customWidth="1"/>
+    <col min="17" max="32" width="9.11111111111111" style="2"/>
     <col min="33" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -2984,7 +3136,7 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3034,7 +3186,7 @@
       <c r="O2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3084,7 +3236,7 @@
       <c r="O3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3134,7 +3286,7 @@
       <c r="O4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="P4" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3184,7 +3336,7 @@
       <c r="O5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="P5" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3234,7 +3386,7 @@
       <c r="O6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="P6" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3284,7 +3436,7 @@
       <c r="O7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="P7" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3334,7 +3486,7 @@
       <c r="O8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P8" s="2" t="s">
+      <c r="P8" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3384,7 +3536,7 @@
       <c r="O9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="P9" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3434,7 +3586,7 @@
       <c r="O10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P10" s="2" t="s">
+      <c r="P10" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3484,7 +3636,7 @@
       <c r="O11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P11" s="2" t="s">
+      <c r="P11" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3534,7 +3686,7 @@
       <c r="O12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P12" s="2" t="s">
+      <c r="P12" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3584,6 +3736,7 @@
       <c r="O13" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="P13" s="5"/>
     </row>
     <row r="14" s="2" customFormat="1" spans="1:16">
       <c r="A14" s="2">
@@ -3631,7 +3784,7 @@
       <c r="O14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P14" s="2" t="s">
+      <c r="P14" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3681,7 +3834,7 @@
       <c r="O15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P15" s="2" t="s">
+      <c r="P15" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3731,7 +3884,7 @@
       <c r="O16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P16" s="2" t="s">
+      <c r="P16" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3781,7 +3934,7 @@
       <c r="O17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P17" s="2" t="s">
+      <c r="P17" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3831,7 +3984,7 @@
       <c r="O18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P18" s="2" t="s">
+      <c r="P18" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3881,7 +4034,7 @@
       <c r="O19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P19" s="2" t="s">
+      <c r="P19" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3931,7 +4084,7 @@
       <c r="O20" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P20" s="2" t="s">
+      <c r="P20" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3981,7 +4134,7 @@
       <c r="O21" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P21" s="2" t="s">
+      <c r="P21" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4031,7 +4184,7 @@
       <c r="O22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P22" s="2" t="s">
+      <c r="P22" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4081,7 +4234,7 @@
       <c r="O23" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P23" s="2" t="s">
+      <c r="P23" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4131,7 +4284,7 @@
       <c r="O24" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P24" s="2" t="s">
+      <c r="P24" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4181,7 +4334,7 @@
       <c r="O25" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P25" s="2" t="s">
+      <c r="P25" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4231,7 +4384,7 @@
       <c r="O26" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P26" s="2" t="s">
+      <c r="P26" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4281,7 +4434,7 @@
       <c r="O27" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P27" s="2" t="s">
+      <c r="P27" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4331,7 +4484,7 @@
       <c r="O28" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P28" s="2" t="s">
+      <c r="P28" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4381,11 +4534,11 @@
       <c r="O29" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P29" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:16">
+      <c r="P29" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" ht="90" spans="1:16">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -4428,10 +4581,10 @@
       <c r="N30" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="O30" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="P30" s="2" t="s">
+      <c r="O30" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="P30" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4440,13 +4593,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>19</v>
@@ -4461,7 +4614,7 @@
         <v>2</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J31" s="2">
         <v>0.001</v>
@@ -4473,15 +4626,15 @@
         <v>19</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P31" s="2" t="s">
+      <c r="P31" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4490,13 +4643,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>19</v>
@@ -4511,7 +4664,7 @@
         <v>2</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J32" s="2">
         <v>0.001</v>
@@ -4523,15 +4676,15 @@
         <v>19</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P32" s="2" t="s">
+      <c r="P32" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4540,13 +4693,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>19</v>
@@ -4561,7 +4714,7 @@
         <v>2</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J33" s="2">
         <v>0.001</v>
@@ -4573,15 +4726,15 @@
         <v>19</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P33" s="2" t="s">
+      <c r="P33" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4590,13 +4743,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>19</v>
@@ -4611,7 +4764,7 @@
         <v>2</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J34" s="2">
         <v>0.001</v>
@@ -4623,15 +4776,15 @@
         <v>19</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P34" s="2" t="s">
+      <c r="P34" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4640,7 +4793,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>17</v>
@@ -4673,15 +4826,15 @@
         <v>19</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P35" s="2" t="s">
+      <c r="P35" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4690,7 +4843,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>17</v>
@@ -4723,15 +4876,15 @@
         <v>19</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P36" s="2" t="s">
+      <c r="P36" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4740,7 +4893,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>17</v>
@@ -4773,15 +4926,15 @@
         <v>19</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P37" s="2" t="s">
+      <c r="P37" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4790,7 +4943,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>17</v>
@@ -4823,15 +4976,15 @@
         <v>19</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P38" s="2" t="s">
+      <c r="P38" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4840,7 +4993,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>17</v>
@@ -4873,15 +5026,15 @@
         <v>19</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P39" s="2" t="s">
+      <c r="P39" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4890,7 +5043,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>17</v>
@@ -4923,15 +5076,15 @@
         <v>19</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P40" s="2" t="s">
+      <c r="P40" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4940,7 +5093,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>17</v>
@@ -4973,15 +5126,15 @@
         <v>19</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P41" s="2" t="s">
+      <c r="P41" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4990,7 +5143,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>17</v>
@@ -5023,15 +5176,15 @@
         <v>19</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P42" s="2" t="s">
+      <c r="P42" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5040,7 +5193,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>17</v>
@@ -5073,15 +5226,15 @@
         <v>19</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P43" s="2" t="s">
+      <c r="P43" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5090,7 +5243,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>17</v>
@@ -5123,15 +5276,15 @@
         <v>19</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P44" s="2" t="s">
+      <c r="P44" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5140,7 +5293,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>17</v>
@@ -5173,15 +5326,15 @@
         <v>19</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P45" s="2" t="s">
+      <c r="P45" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5190,7 +5343,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>17</v>
@@ -5223,15 +5376,15 @@
         <v>19</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P46" s="2" t="s">
+      <c r="P46" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5240,7 +5393,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>17</v>
@@ -5273,15 +5426,15 @@
         <v>19</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P47" s="2" t="s">
+      <c r="P47" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5290,7 +5443,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>17</v>
@@ -5323,15 +5476,15 @@
         <v>19</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P48" s="2" t="s">
+      <c r="P48" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5340,7 +5493,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>17</v>
@@ -5373,15 +5526,15 @@
         <v>19</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P49" s="2" t="s">
+      <c r="P49" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5390,7 +5543,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>17</v>
@@ -5423,15 +5576,15 @@
         <v>19</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P50" s="2" t="s">
+      <c r="P50" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5440,7 +5593,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>17</v>
@@ -5473,15 +5626,15 @@
         <v>19</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P51" s="2" t="s">
+      <c r="P51" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5490,7 +5643,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>17</v>
@@ -5523,15 +5676,15 @@
         <v>19</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P52" s="2" t="s">
+      <c r="P52" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5540,7 +5693,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>17</v>
@@ -5573,15 +5726,15 @@
         <v>19</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P53" s="2" t="s">
+      <c r="P53" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5590,7 +5743,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>17</v>
@@ -5623,15 +5776,15 @@
         <v>19</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P54" s="2" t="s">
+      <c r="P54" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5640,7 +5793,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>17</v>
@@ -5673,15 +5826,15 @@
         <v>19</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O55" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P55" s="2" t="s">
+      <c r="P55" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5690,7 +5843,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>17</v>
@@ -5723,15 +5876,15 @@
         <v>19</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P56" s="2" t="s">
+      <c r="P56" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5740,7 +5893,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>17</v>
@@ -5776,12 +5929,12 @@
         <v>19</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P57" s="2" t="s">
+      <c r="P57" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5790,7 +5943,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>17</v>
@@ -5823,15 +5976,15 @@
         <v>19</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P58" s="2" t="s">
+      <c r="P58" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5840,7 +5993,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>17</v>
@@ -5873,15 +6026,15 @@
         <v>19</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O59" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P59" s="2" t="s">
+      <c r="P59" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5890,7 +6043,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>31</v>
@@ -5923,15 +6076,15 @@
         <v>19</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O60" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P60" s="2" t="s">
+      <c r="P60" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5940,7 +6093,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>31</v>
@@ -5973,15 +6126,15 @@
         <v>19</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O61" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P61" s="2" t="s">
+      <c r="P61" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5990,7 +6143,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>31</v>
@@ -6023,15 +6176,15 @@
         <v>19</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P62" s="2" t="s">
+      <c r="P62" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6040,7 +6193,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>31</v>
@@ -6073,15 +6226,15 @@
         <v>19</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P63" s="2" t="s">
+      <c r="P63" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6090,7 +6243,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>31</v>
@@ -6123,15 +6276,15 @@
         <v>19</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P64" s="2" t="s">
+      <c r="P64" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6140,7 +6293,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>31</v>
@@ -6173,15 +6326,15 @@
         <v>19</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O65" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P65" s="2" t="s">
+      <c r="P65" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6190,7 +6343,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>31</v>
@@ -6219,19 +6372,19 @@
       <c r="K66" s="3">
         <v>0</v>
       </c>
-      <c r="L66" s="7">
+      <c r="L66" s="10">
         <v>0</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P66" s="3" t="s">
+      <c r="P66" s="11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6240,7 +6393,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>31</v>
@@ -6269,19 +6422,19 @@
       <c r="K67" s="3">
         <v>0</v>
       </c>
-      <c r="L67" s="7">
+      <c r="L67" s="10">
         <v>0</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O67" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P67" s="3" t="s">
+      <c r="P67" s="11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6290,7 +6443,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>17</v>
@@ -6323,15 +6476,15 @@
         <v>19</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O68" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P68" s="2" t="s">
+      <c r="P68" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6340,7 +6493,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>17</v>
@@ -6373,15 +6526,15 @@
         <v>19</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O69" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P69" s="2" t="s">
+      <c r="P69" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6390,7 +6543,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>17</v>
@@ -6423,15 +6576,15 @@
         <v>19</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O70" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P70" s="2" t="s">
+      <c r="P70" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6440,7 +6593,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>17</v>
@@ -6473,15 +6626,15 @@
         <v>19</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O71" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P71" s="2" t="s">
+      <c r="P71" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6490,7 +6643,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>17</v>
@@ -6523,15 +6676,15 @@
         <v>19</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P72" s="2" t="s">
+      <c r="P72" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6540,7 +6693,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>17</v>
@@ -6573,15 +6726,15 @@
         <v>19</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O73" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P73" s="2" t="s">
+      <c r="P73" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6590,7 +6743,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>17</v>
@@ -6623,15 +6776,15 @@
         <v>19</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O74" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P74" s="2" t="s">
+      <c r="P74" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6640,7 +6793,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>17</v>
@@ -6673,15 +6826,15 @@
         <v>19</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O75" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P75" s="2" t="s">
+      <c r="P75" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6690,7 +6843,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>17</v>
@@ -6723,15 +6876,15 @@
         <v>19</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O76" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P76" s="2" t="s">
+      <c r="P76" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6740,7 +6893,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>17</v>
@@ -6773,15 +6926,15 @@
         <v>19</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O77" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P77" s="2" t="s">
+      <c r="P77" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6790,7 +6943,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>17</v>
@@ -6823,15 +6976,15 @@
         <v>19</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O78" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P78" s="2" t="s">
+      <c r="P78" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6840,7 +6993,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>17</v>
@@ -6873,15 +7026,15 @@
         <v>19</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O79" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P79" s="2" t="s">
+      <c r="P79" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6890,13 +7043,13 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>19</v>
@@ -6923,15 +7076,15 @@
         <v>19</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P80" s="2" t="s">
+      <c r="P80" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6940,13 +7093,13 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>19</v>
@@ -6973,15 +7126,15 @@
         <v>19</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O81" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P81" s="2" t="s">
+      <c r="P81" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6990,13 +7143,13 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>19</v>
@@ -7023,15 +7176,15 @@
         <v>19</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O82" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P82" s="2" t="s">
+      <c r="P82" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7040,7 +7193,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>17</v>
@@ -7073,15 +7226,15 @@
         <v>19</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O83" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P83" s="2" t="s">
+      <c r="P83" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7090,7 +7243,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>31</v>
@@ -7123,15 +7276,15 @@
         <v>19</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O84" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P84" s="2" t="s">
+      <c r="P84" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7140,13 +7293,13 @@
         <v>84</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>19</v>
@@ -7173,15 +7326,15 @@
         <v>19</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O85" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P85" s="2" t="s">
+      <c r="P85" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7190,13 +7343,13 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>19</v>
@@ -7223,15 +7376,15 @@
         <v>19</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O86" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P86" s="2" t="s">
+      <c r="P86" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7240,7 +7393,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>17</v>
@@ -7273,15 +7426,15 @@
         <v>19</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O87" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P87" s="2" t="s">
+      <c r="P87" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7290,7 +7443,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>17</v>
@@ -7323,15 +7476,15 @@
         <v>19</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O88" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P88" s="2" t="s">
+      <c r="P88" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7340,9 +7493,9 @@
         <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C89" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C89" s="9" t="s">
         <v>31</v>
       </c>
       <c r="D89" s="2" t="s">
@@ -7373,15 +7526,15 @@
         <v>19</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O89" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P89" s="2" t="s">
+      <c r="P89" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7390,9 +7543,9 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C90" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="C90" s="9" t="s">
         <v>31</v>
       </c>
       <c r="D90" s="2" t="s">
@@ -7423,15 +7576,15 @@
         <v>19</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O90" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P90" s="2" t="s">
+      <c r="P90" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7440,7 +7593,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>17</v>
@@ -7473,15 +7626,15 @@
         <v>19</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O91" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P91" s="2" t="s">
+      <c r="P91" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7490,7 +7643,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>17</v>
@@ -7523,15 +7676,15 @@
         <v>19</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O92" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P92" s="2" t="s">
+      <c r="P92" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7540,7 +7693,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>17</v>
@@ -7569,19 +7722,19 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="7">
+      <c r="L93" s="10">
         <v>0</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N93" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O93" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P93" s="3" t="s">
+      <c r="P93" s="11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7590,7 +7743,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>17</v>
@@ -7619,19 +7772,19 @@
       <c r="K94" s="3">
         <v>0</v>
       </c>
-      <c r="L94" s="7">
+      <c r="L94" s="10">
         <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N94" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P94" s="3" t="s">
+      <c r="P94" s="11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7640,7 +7793,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>17</v>
@@ -7669,19 +7822,19 @@
       <c r="K95" s="3">
         <v>0</v>
       </c>
-      <c r="L95" s="7">
+      <c r="L95" s="10">
         <v>0</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N95" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O95" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P95" s="3" t="s">
+      <c r="P95" s="11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7690,7 +7843,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>17</v>
@@ -7719,19 +7872,19 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-      <c r="L96" s="7">
+      <c r="L96" s="10">
         <v>0</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N96" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O96" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P96" s="3" t="s">
+      <c r="P96" s="11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7740,7 +7893,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>17</v>
@@ -7769,19 +7922,19 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="7">
+      <c r="L97" s="10">
         <v>0</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O97" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P97" s="3" t="s">
+      <c r="P97" s="11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7790,7 +7943,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>17</v>
@@ -7823,15 +7976,15 @@
         <v>19</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O98" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P98" s="2" t="s">
+      <c r="P98" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7840,7 +7993,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>17</v>
@@ -7873,15 +8026,15 @@
         <v>19</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O99" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P99" s="2" t="s">
+      <c r="P99" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7890,7 +8043,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>17</v>
@@ -7926,12 +8079,12 @@
         <v>19</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O100" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P100" s="2" t="s">
+      <c r="P100" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7940,7 +8093,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>17</v>
@@ -7973,15 +8126,15 @@
         <v>19</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O101" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P101" s="2" t="s">
+      <c r="P101" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7990,7 +8143,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>17</v>
@@ -8023,15 +8176,15 @@
         <v>19</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O102" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P102" s="2" t="s">
+      <c r="P102" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8040,7 +8193,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>17</v>
@@ -8073,15 +8226,15 @@
         <v>19</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O103" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P103" s="2" t="s">
+      <c r="P103" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8090,7 +8243,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>17</v>
@@ -8123,15 +8276,15 @@
         <v>19</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O104" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P104" s="2" t="s">
+      <c r="P104" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8140,7 +8293,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>17</v>
@@ -8173,15 +8326,15 @@
         <v>19</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O105" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P105" s="2" t="s">
+      <c r="P105" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8190,7 +8343,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>17</v>
@@ -8223,15 +8376,15 @@
         <v>19</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O106" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P106" s="2" t="s">
+      <c r="P106" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8240,7 +8393,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>17</v>
@@ -8273,15 +8426,15 @@
         <v>19</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O107" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P107" s="2" t="s">
+      <c r="P107" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8290,7 +8443,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>17</v>
@@ -8323,15 +8476,15 @@
         <v>19</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O108" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P108" s="2" t="s">
+      <c r="P108" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8340,7 +8493,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>17</v>
@@ -8373,15 +8526,15 @@
         <v>19</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O109" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P109" s="2" t="s">
+      <c r="P109" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8390,7 +8543,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>17</v>
@@ -8423,15 +8576,15 @@
         <v>19</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N110" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O110" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P110" s="2" t="s">
+      <c r="P110" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8440,7 +8593,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>17</v>
@@ -8473,15 +8626,15 @@
         <v>19</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O111" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P111" s="2" t="s">
+      <c r="P111" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8490,7 +8643,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>17</v>
@@ -8523,15 +8676,15 @@
         <v>19</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O112" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P112" s="2" t="s">
+      <c r="P112" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8540,7 +8693,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>17</v>
@@ -8573,15 +8726,15 @@
         <v>19</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N113" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O113" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P113" s="2" t="s">
+      <c r="P113" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8590,7 +8743,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>17</v>
@@ -8623,15 +8776,15 @@
         <v>19</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O114" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P114" s="2" t="s">
+      <c r="P114" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8640,7 +8793,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>17</v>
@@ -8673,15 +8826,15 @@
         <v>19</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N115" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O115" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P115" s="2" t="s">
+      <c r="P115" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8690,7 +8843,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>17</v>
@@ -8723,15 +8876,15 @@
         <v>19</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N116" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O116" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P116" s="2" t="s">
+      <c r="P116" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8740,7 +8893,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>17</v>
@@ -8773,15 +8926,15 @@
         <v>19</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N117" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O117" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P117" s="2" t="s">
+      <c r="P117" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8790,7 +8943,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>17</v>
@@ -8823,15 +8976,15 @@
         <v>19</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O118" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P118" s="2" t="s">
+      <c r="P118" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8840,7 +8993,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>17</v>
@@ -8873,15 +9026,15 @@
         <v>19</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O119" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P119" s="2" t="s">
+      <c r="P119" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8890,7 +9043,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>17</v>
@@ -8923,15 +9076,15 @@
         <v>19</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O120" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P120" s="2" t="s">
+      <c r="P120" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8940,7 +9093,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>17</v>
@@ -8973,15 +9126,15 @@
         <v>19</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N121" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O121" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P121" s="2" t="s">
+      <c r="P121" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8990,7 +9143,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>17</v>
@@ -9023,15 +9176,15 @@
         <v>19</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N122" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O122" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P122" s="2" t="s">
+      <c r="P122" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9040,7 +9193,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>17</v>
@@ -9073,15 +9226,15 @@
         <v>19</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N123" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O123" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P123" s="2" t="s">
+      <c r="P123" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9090,7 +9243,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>17</v>
@@ -9123,15 +9276,15 @@
         <v>19</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O124" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P124" s="2" t="s">
+      <c r="P124" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9140,7 +9293,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>17</v>
@@ -9173,15 +9326,15 @@
         <v>19</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N125" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O125" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P125" s="2" t="s">
+      <c r="P125" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9190,7 +9343,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>17</v>
@@ -9223,15 +9376,15 @@
         <v>19</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N126" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O126" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P126" s="2" t="s">
+      <c r="P126" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9240,7 +9393,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>17</v>
@@ -9273,15 +9426,15 @@
         <v>19</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N127" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O127" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P127" s="2" t="s">
+      <c r="P127" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9290,7 +9443,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>17</v>
@@ -9323,15 +9476,15 @@
         <v>19</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O128" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P128" s="2" t="s">
+      <c r="P128" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9340,7 +9493,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>17</v>
@@ -9373,15 +9526,15 @@
         <v>19</v>
       </c>
       <c r="M129" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N129" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O129" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P129" s="2" t="s">
+      <c r="P129" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9390,7 +9543,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>17</v>
@@ -9423,15 +9576,15 @@
         <v>19</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N130" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O130" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P130" s="2" t="s">
+      <c r="P130" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9440,7 +9593,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>17</v>
@@ -9473,15 +9626,15 @@
         <v>19</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N131" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O131" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P131" s="2" t="s">
+      <c r="P131" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9490,7 +9643,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>17</v>
@@ -9523,15 +9676,15 @@
         <v>19</v>
       </c>
       <c r="M132" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N132" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O132" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P132" s="2" t="s">
+      <c r="P132" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9540,7 +9693,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>17</v>
@@ -9573,15 +9726,15 @@
         <v>19</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N133" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O133" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P133" s="2" t="s">
+      <c r="P133" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9590,7 +9743,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>17</v>
@@ -9623,15 +9776,15 @@
         <v>19</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N134" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O134" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P134" s="2" t="s">
+      <c r="P134" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9640,7 +9793,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>31</v>
@@ -9673,15 +9826,15 @@
         <v>19</v>
       </c>
       <c r="M135" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N135" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O135" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P135" s="2" t="s">
+      <c r="P135" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9690,7 +9843,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>31</v>
@@ -9723,15 +9876,15 @@
         <v>19</v>
       </c>
       <c r="M136" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N136" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O136" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P136" s="2" t="s">
+      <c r="P136" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9740,7 +9893,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>31</v>
@@ -9773,15 +9926,15 @@
         <v>19</v>
       </c>
       <c r="M137" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N137" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O137" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P137" s="2" t="s">
+      <c r="P137" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9790,7 +9943,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>17</v>
@@ -9823,15 +9976,15 @@
         <v>19</v>
       </c>
       <c r="M138" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N138" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O138" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P138" s="2" t="s">
+      <c r="P138" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9840,13 +9993,13 @@
         <v>138</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>19</v>
@@ -9857,31 +10010,31 @@
       <c r="G139" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H139" s="6">
-        <v>1</v>
-      </c>
-      <c r="I139" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J139" s="6">
-        <v>1</v>
-      </c>
-      <c r="K139" s="6">
+      <c r="H139" s="9">
+        <v>1</v>
+      </c>
+      <c r="I139" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J139" s="9">
+        <v>1</v>
+      </c>
+      <c r="K139" s="9">
         <v>0</v>
       </c>
       <c r="L139" s="2" t="s">
         <v>19</v>
       </c>
       <c r="M139" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N139" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O139" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P139" s="2" t="s">
+      <c r="P139" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9890,7 +10043,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>31</v>
@@ -9923,15 +10076,15 @@
         <v>19</v>
       </c>
       <c r="M140" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N140" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O140" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P140" s="2" t="s">
+      <c r="P140" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9940,7 +10093,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>31</v>
@@ -9973,15 +10126,15 @@
         <v>19</v>
       </c>
       <c r="M141" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N141" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O141" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P141" s="2" t="s">
+      <c r="P141" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9990,7 +10143,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>31</v>
@@ -10023,15 +10176,15 @@
         <v>19</v>
       </c>
       <c r="M142" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N142" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O142" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P142" s="2" t="s">
+      <c r="P142" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10040,7 +10193,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>31</v>
@@ -10073,15 +10226,15 @@
         <v>19</v>
       </c>
       <c r="M143" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N143" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O143" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P143" s="2" t="s">
+      <c r="P143" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10090,7 +10243,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>31</v>
@@ -10123,15 +10276,15 @@
         <v>19</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N144" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O144" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P144" s="2" t="s">
+      <c r="P144" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10140,7 +10293,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>31</v>
@@ -10173,15 +10326,15 @@
         <v>19</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N145" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O145" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P145" s="2" t="s">
+      <c r="P145" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10190,7 +10343,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>31</v>
@@ -10223,15 +10376,15 @@
         <v>19</v>
       </c>
       <c r="M146" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N146" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O146" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P146" s="2" t="s">
+      <c r="P146" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10240,7 +10393,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>31</v>
@@ -10273,15 +10426,15 @@
         <v>19</v>
       </c>
       <c r="M147" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N147" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O147" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P147" s="2" t="s">
+      <c r="P147" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10290,7 +10443,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>31</v>
@@ -10323,15 +10476,15 @@
         <v>19</v>
       </c>
       <c r="M148" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N148" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O148" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P148" s="2" t="s">
+      <c r="P148" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10340,7 +10493,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>31</v>
@@ -10373,15 +10526,15 @@
         <v>19</v>
       </c>
       <c r="M149" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N149" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O149" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P149" s="2" t="s">
+      <c r="P149" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10390,7 +10543,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>31</v>
@@ -10423,15 +10576,15 @@
         <v>19</v>
       </c>
       <c r="M150" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N150" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O150" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P150" s="2" t="s">
+      <c r="P150" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10440,7 +10593,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>31</v>
@@ -10473,15 +10626,15 @@
         <v>19</v>
       </c>
       <c r="M151" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N151" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O151" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P151" s="2" t="s">
+      <c r="P151" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10490,7 +10643,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>31</v>
@@ -10523,15 +10676,15 @@
         <v>19</v>
       </c>
       <c r="M152" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N152" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O152" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P152" s="2" t="s">
+      <c r="P152" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10540,7 +10693,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>31</v>
@@ -10573,15 +10726,15 @@
         <v>19</v>
       </c>
       <c r="M153" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N153" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O153" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P153" s="2" t="s">
+      <c r="P153" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10590,7 +10743,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>31</v>
@@ -10623,15 +10776,15 @@
         <v>19</v>
       </c>
       <c r="M154" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N154" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O154" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P154" s="2" t="s">
+      <c r="P154" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10640,7 +10793,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>31</v>
@@ -10673,15 +10826,15 @@
         <v>19</v>
       </c>
       <c r="M155" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N155" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O155" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P155" s="2" t="s">
+      <c r="P155" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10690,7 +10843,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>31</v>
@@ -10723,24 +10876,24 @@
         <v>19</v>
       </c>
       <c r="M156" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N156" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O156" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P156" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="157" s="2" customFormat="1" spans="1:16">
+      <c r="P156" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="157" s="2" customFormat="1" ht="288" spans="1:16">
       <c r="A157" s="2">
         <v>156</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>17</v>
@@ -10773,24 +10926,24 @@
         <v>19</v>
       </c>
       <c r="M157" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N157" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O157" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P157" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="158" s="2" customFormat="1" spans="1:16">
+      <c r="P157" s="8" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="158" s="2" customFormat="1" ht="288" spans="1:16">
       <c r="A158" s="2">
         <v>157</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>17</v>
@@ -10823,24 +10976,24 @@
         <v>19</v>
       </c>
       <c r="M158" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N158" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="O158" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P158" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="159" s="2" customFormat="1" spans="1:16">
+      <c r="P158" s="8" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="159" s="2" customFormat="1" ht="288" spans="1:16">
       <c r="A159" s="2">
         <v>158</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>17</v>
@@ -10857,40 +11010,40 @@
       <c r="G159" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H159" s="6">
-        <v>1</v>
-      </c>
-      <c r="I159" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J159" s="6">
-        <v>1</v>
-      </c>
-      <c r="K159" s="6">
+      <c r="H159" s="9">
+        <v>1</v>
+      </c>
+      <c r="I159" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J159" s="9">
+        <v>1</v>
+      </c>
+      <c r="K159" s="9">
         <v>0</v>
       </c>
       <c r="L159" s="2" t="s">
         <v>19</v>
       </c>
       <c r="M159" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="N159" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="O159" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P159" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="160" s="2" customFormat="1" spans="1:16">
+      <c r="P159" s="8" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="160" s="2" customFormat="1" ht="288" spans="1:16">
       <c r="A160" s="2">
         <v>159</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>17</v>
@@ -10907,40 +11060,40 @@
       <c r="G160" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H160" s="6">
-        <v>1</v>
-      </c>
-      <c r="I160" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J160" s="6">
-        <v>1</v>
-      </c>
-      <c r="K160" s="6">
+      <c r="H160" s="9">
+        <v>1</v>
+      </c>
+      <c r="I160" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J160" s="9">
+        <v>1</v>
+      </c>
+      <c r="K160" s="9">
         <v>0</v>
       </c>
       <c r="L160" s="2" t="s">
         <v>19</v>
       </c>
       <c r="M160" s="2" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="N160" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="O160" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P160" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="161" s="2" customFormat="1" spans="1:16">
+      <c r="P160" s="8" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="161" s="2" customFormat="1" ht="288" spans="1:16">
       <c r="A161" s="2">
         <v>160</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>17</v>
@@ -10957,32 +11110,32 @@
       <c r="G161" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H161" s="6">
-        <v>1</v>
-      </c>
-      <c r="I161" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J161" s="6">
-        <v>1</v>
-      </c>
-      <c r="K161" s="6">
+      <c r="H161" s="9">
+        <v>1</v>
+      </c>
+      <c r="I161" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J161" s="9">
+        <v>1</v>
+      </c>
+      <c r="K161" s="9">
         <v>0</v>
       </c>
       <c r="L161" s="2" t="s">
         <v>19</v>
       </c>
       <c r="M161" s="2" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="N161" s="2" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="O161" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P161" s="2" t="s">
-        <v>19</v>
+      <c r="P161" s="8" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="162" s="3" customFormat="1" spans="1:16">
@@ -10990,7 +11143,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>17</v>
@@ -11007,31 +11160,31 @@
       <c r="G162" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H162" s="7">
-        <v>1</v>
-      </c>
-      <c r="I162" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J162" s="7">
-        <v>1</v>
-      </c>
-      <c r="K162" s="7">
-        <v>0</v>
-      </c>
-      <c r="L162" s="7">
+      <c r="H162" s="10">
+        <v>1</v>
+      </c>
+      <c r="I162" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J162" s="10">
+        <v>1</v>
+      </c>
+      <c r="K162" s="10">
+        <v>0</v>
+      </c>
+      <c r="L162" s="10">
         <v>0</v>
       </c>
       <c r="M162" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N162" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O162" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P162" s="3" t="s">
+      <c r="P162" s="11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11040,7 +11193,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C163" s="3" t="s">
         <v>17</v>
@@ -11057,31 +11210,31 @@
       <c r="G163" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H163" s="7">
-        <v>1</v>
-      </c>
-      <c r="I163" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J163" s="7">
-        <v>1</v>
-      </c>
-      <c r="K163" s="7">
-        <v>0</v>
-      </c>
-      <c r="L163" s="7">
+      <c r="H163" s="10">
+        <v>1</v>
+      </c>
+      <c r="I163" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J163" s="10">
+        <v>1</v>
+      </c>
+      <c r="K163" s="10">
+        <v>0</v>
+      </c>
+      <c r="L163" s="10">
         <v>0</v>
       </c>
       <c r="M163" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N163" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O163" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P163" s="3" t="s">
+      <c r="P163" s="11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11090,7 +11243,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>17</v>
@@ -11107,40 +11260,40 @@
       <c r="G164" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H164" s="7">
-        <v>1</v>
-      </c>
-      <c r="I164" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J164" s="7">
-        <v>1</v>
-      </c>
-      <c r="K164" s="7">
-        <v>0</v>
-      </c>
-      <c r="L164" s="7">
+      <c r="H164" s="10">
+        <v>1</v>
+      </c>
+      <c r="I164" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J164" s="10">
+        <v>1</v>
+      </c>
+      <c r="K164" s="10">
+        <v>0</v>
+      </c>
+      <c r="L164" s="10">
         <v>0</v>
       </c>
       <c r="M164" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N164" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O164" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P164" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="165" s="2" customFormat="1" spans="1:16">
+      <c r="P164" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="165" s="2" customFormat="1" ht="378" spans="1:16">
       <c r="A165" s="2">
         <v>164</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>17</v>
@@ -11157,40 +11310,40 @@
       <c r="G165" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H165" s="6">
-        <v>1</v>
-      </c>
-      <c r="I165" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J165" s="6">
-        <v>1</v>
-      </c>
-      <c r="K165" s="6">
+      <c r="H165" s="9">
+        <v>1</v>
+      </c>
+      <c r="I165" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J165" s="9">
+        <v>1</v>
+      </c>
+      <c r="K165" s="9">
         <v>0</v>
       </c>
       <c r="L165" s="2" t="s">
         <v>19</v>
       </c>
       <c r="M165" s="2" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="N165" s="2" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="O165" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P165" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="166" s="2" customFormat="1" spans="1:16">
+      <c r="P165" s="8" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="166" s="2" customFormat="1" ht="306" spans="1:16">
       <c r="A166" s="2">
         <v>165</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>17</v>
@@ -11207,32 +11360,32 @@
       <c r="G166" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H166" s="6">
-        <v>1</v>
-      </c>
-      <c r="I166" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J166" s="6">
-        <v>1</v>
-      </c>
-      <c r="K166" s="6">
+      <c r="H166" s="9">
+        <v>1</v>
+      </c>
+      <c r="I166" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J166" s="9">
+        <v>1</v>
+      </c>
+      <c r="K166" s="9">
         <v>0</v>
       </c>
       <c r="L166" s="2" t="s">
         <v>19</v>
       </c>
       <c r="M166" s="2" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="N166" s="2" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="O166" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P166" s="2" t="s">
-        <v>19</v>
+      <c r="P166" s="8" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="167" s="2" customFormat="1" spans="1:16">
@@ -11240,7 +11393,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>17</v>
@@ -11257,31 +11410,31 @@
       <c r="G167" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H167" s="6">
-        <v>1</v>
-      </c>
-      <c r="I167" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J167" s="6">
-        <v>1</v>
-      </c>
-      <c r="K167" s="6">
+      <c r="H167" s="9">
+        <v>1</v>
+      </c>
+      <c r="I167" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J167" s="9">
+        <v>1</v>
+      </c>
+      <c r="K167" s="9">
         <v>0</v>
       </c>
       <c r="L167" s="2" t="s">
         <v>19</v>
       </c>
       <c r="M167" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="N167" s="2" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="O167" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P167" s="2" t="s">
+      <c r="P167" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11290,7 +11443,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>17</v>
@@ -11307,31 +11460,31 @@
       <c r="G168" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H168" s="6">
-        <v>1</v>
-      </c>
-      <c r="I168" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J168" s="6">
-        <v>1</v>
-      </c>
-      <c r="K168" s="6">
+      <c r="H168" s="9">
+        <v>1</v>
+      </c>
+      <c r="I168" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J168" s="9">
+        <v>1</v>
+      </c>
+      <c r="K168" s="9">
         <v>0</v>
       </c>
       <c r="L168" s="2" t="s">
         <v>19</v>
       </c>
       <c r="M168" s="2" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="N168" s="2" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="O168" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P168" s="2" t="s">
+      <c r="P168" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11340,7 +11493,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>17</v>
@@ -11357,31 +11510,31 @@
       <c r="G169" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H169" s="6">
-        <v>1</v>
-      </c>
-      <c r="I169" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J169" s="6">
-        <v>1</v>
-      </c>
-      <c r="K169" s="6">
+      <c r="H169" s="9">
+        <v>1</v>
+      </c>
+      <c r="I169" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J169" s="9">
+        <v>1</v>
+      </c>
+      <c r="K169" s="9">
         <v>0</v>
       </c>
       <c r="L169" s="2" t="s">
         <v>19</v>
       </c>
       <c r="M169" s="2" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="N169" s="2" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="O169" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P169" s="2" t="s">
+      <c r="P169" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11390,7 +11543,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>17</v>
@@ -11407,31 +11560,31 @@
       <c r="G170" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H170" s="6">
-        <v>1</v>
-      </c>
-      <c r="I170" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J170" s="6">
-        <v>1</v>
-      </c>
-      <c r="K170" s="6">
+      <c r="H170" s="9">
+        <v>1</v>
+      </c>
+      <c r="I170" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J170" s="9">
+        <v>1</v>
+      </c>
+      <c r="K170" s="9">
         <v>0</v>
       </c>
       <c r="L170" s="2" t="s">
         <v>19</v>
       </c>
       <c r="M170" s="2" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="N170" s="2" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="O170" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P170" s="2" t="s">
+      <c r="P170" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11440,7 +11593,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>17</v>
@@ -11457,31 +11610,31 @@
       <c r="G171" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H171" s="6">
-        <v>1</v>
-      </c>
-      <c r="I171" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J171" s="6">
-        <v>1</v>
-      </c>
-      <c r="K171" s="6">
+      <c r="H171" s="9">
+        <v>1</v>
+      </c>
+      <c r="I171" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J171" s="9">
+        <v>1</v>
+      </c>
+      <c r="K171" s="9">
         <v>0</v>
       </c>
       <c r="L171" s="2" t="s">
         <v>19</v>
       </c>
       <c r="M171" s="2" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="N171" s="2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="O171" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P171" s="2" t="s">
+      <c r="P171" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11490,7 +11643,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>17</v>
@@ -11507,31 +11660,31 @@
       <c r="G172" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H172" s="6">
-        <v>1</v>
-      </c>
-      <c r="I172" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J172" s="6">
-        <v>1</v>
-      </c>
-      <c r="K172" s="6">
+      <c r="H172" s="9">
+        <v>1</v>
+      </c>
+      <c r="I172" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J172" s="9">
+        <v>1</v>
+      </c>
+      <c r="K172" s="9">
         <v>0</v>
       </c>
       <c r="L172" s="2" t="s">
         <v>19</v>
       </c>
       <c r="M172" s="2" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="N172" s="2" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="O172" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P172" s="2" t="s">
+      <c r="P172" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11540,7 +11693,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>17</v>
@@ -11557,31 +11710,31 @@
       <c r="G173" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H173" s="6">
-        <v>1</v>
-      </c>
-      <c r="I173" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J173" s="6">
-        <v>1</v>
-      </c>
-      <c r="K173" s="6">
+      <c r="H173" s="9">
+        <v>1</v>
+      </c>
+      <c r="I173" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J173" s="9">
+        <v>1</v>
+      </c>
+      <c r="K173" s="9">
         <v>0</v>
       </c>
       <c r="L173" s="2" t="s">
         <v>19</v>
       </c>
       <c r="M173" s="2" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="N173" s="2" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="O173" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P173" s="2" t="s">
+      <c r="P173" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11590,7 +11743,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>17</v>
@@ -11607,31 +11760,31 @@
       <c r="G174" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H174" s="6">
-        <v>1</v>
-      </c>
-      <c r="I174" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J174" s="6">
-        <v>1</v>
-      </c>
-      <c r="K174" s="6">
+      <c r="H174" s="9">
+        <v>1</v>
+      </c>
+      <c r="I174" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J174" s="9">
+        <v>1</v>
+      </c>
+      <c r="K174" s="9">
         <v>0</v>
       </c>
       <c r="L174" s="2" t="s">
         <v>19</v>
       </c>
       <c r="M174" s="2" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="N174" s="2" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="O174" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P174" s="2" t="s">
+      <c r="P174" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11640,7 +11793,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C175" s="3" t="s">
         <v>17</v>
@@ -11657,31 +11810,31 @@
       <c r="G175" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H175" s="7">
-        <v>1</v>
-      </c>
-      <c r="I175" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J175" s="7">
-        <v>1</v>
-      </c>
-      <c r="K175" s="7">
-        <v>0</v>
-      </c>
-      <c r="L175" s="7">
+      <c r="H175" s="10">
+        <v>1</v>
+      </c>
+      <c r="I175" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J175" s="10">
+        <v>1</v>
+      </c>
+      <c r="K175" s="10">
+        <v>0</v>
+      </c>
+      <c r="L175" s="10">
         <v>0</v>
       </c>
       <c r="M175" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N175" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O175" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P175" s="3" t="s">
+      <c r="P175" s="11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11690,7 +11843,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C176" s="3" t="s">
         <v>17</v>
@@ -11707,31 +11860,31 @@
       <c r="G176" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H176" s="7">
-        <v>1</v>
-      </c>
-      <c r="I176" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J176" s="7">
-        <v>1</v>
-      </c>
-      <c r="K176" s="7">
-        <v>0</v>
-      </c>
-      <c r="L176" s="7">
+      <c r="H176" s="10">
+        <v>1</v>
+      </c>
+      <c r="I176" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J176" s="10">
+        <v>1</v>
+      </c>
+      <c r="K176" s="10">
+        <v>0</v>
+      </c>
+      <c r="L176" s="10">
         <v>0</v>
       </c>
       <c r="M176" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N176" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O176" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P176" s="3" t="s">
+      <c r="P176" s="11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11740,7 +11893,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>17</v>
@@ -11757,31 +11910,31 @@
       <c r="G177" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H177" s="6">
-        <v>1</v>
-      </c>
-      <c r="I177" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J177" s="6">
-        <v>1</v>
-      </c>
-      <c r="K177" s="6">
+      <c r="H177" s="9">
+        <v>1</v>
+      </c>
+      <c r="I177" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J177" s="9">
+        <v>1</v>
+      </c>
+      <c r="K177" s="9">
         <v>0</v>
       </c>
       <c r="L177" s="2" t="s">
         <v>19</v>
       </c>
       <c r="M177" s="2" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="N177" s="2" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="O177" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P177" s="2" t="s">
+      <c r="P177" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11790,7 +11943,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>17</v>
@@ -11807,31 +11960,31 @@
       <c r="G178" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H178" s="6">
-        <v>1</v>
-      </c>
-      <c r="I178" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J178" s="6">
-        <v>1</v>
-      </c>
-      <c r="K178" s="6">
+      <c r="H178" s="9">
+        <v>1</v>
+      </c>
+      <c r="I178" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J178" s="9">
+        <v>1</v>
+      </c>
+      <c r="K178" s="9">
         <v>0</v>
       </c>
       <c r="L178" s="2" t="s">
         <v>19</v>
       </c>
       <c r="M178" s="2" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="N178" s="2" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="O178" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P178" s="2" t="s">
+      <c r="P178" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11840,7 +11993,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>17</v>
@@ -11857,31 +12010,31 @@
       <c r="G179" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H179" s="6">
-        <v>1</v>
-      </c>
-      <c r="I179" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J179" s="6">
-        <v>1</v>
-      </c>
-      <c r="K179" s="6">
+      <c r="H179" s="9">
+        <v>1</v>
+      </c>
+      <c r="I179" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J179" s="9">
+        <v>1</v>
+      </c>
+      <c r="K179" s="9">
         <v>0</v>
       </c>
       <c r="L179" s="2" t="s">
         <v>19</v>
       </c>
       <c r="M179" s="2" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="N179" s="2" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="O179" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P179" s="2" t="s">
+      <c r="P179" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11890,7 +12043,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>17</v>
@@ -11907,31 +12060,31 @@
       <c r="G180" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H180" s="6">
-        <v>1</v>
-      </c>
-      <c r="I180" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J180" s="6">
-        <v>1</v>
-      </c>
-      <c r="K180" s="6">
+      <c r="H180" s="9">
+        <v>1</v>
+      </c>
+      <c r="I180" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J180" s="9">
+        <v>1</v>
+      </c>
+      <c r="K180" s="9">
         <v>0</v>
       </c>
       <c r="L180" s="2" t="s">
         <v>19</v>
       </c>
       <c r="M180" s="2" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="N180" s="2" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="O180" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P180" s="2" t="s">
+      <c r="P180" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11947,19 +12100,19 @@
   <dimension ref="A1:P17"/>
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="5.4957264957265" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.034188034188" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.94871794871795" style="2" customWidth="1"/>
+    <col min="1" max="1" width="5.49206349206349" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.031746031746" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.95238095238095" style="2" customWidth="1"/>
     <col min="4" max="5" width="5.22222222222222" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.957264957265" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.5897435897436" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.9603174603175" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.5873015873016" style="2" customWidth="1"/>
     <col min="8" max="8" width="5.22222222222222" style="2" customWidth="1"/>
-    <col min="9" max="9" width="11.7435897435897" style="2" customWidth="1"/>
+    <col min="9" max="9" width="11.7460317460317" style="2" customWidth="1"/>
     <col min="10" max="10" width="5.22222222222222" style="2" customWidth="1"/>
-    <col min="11" max="11" width="7.08547008547009" style="2" customWidth="1"/>
+    <col min="11" max="11" width="7.08730158730159" style="2" customWidth="1"/>
     <col min="12" max="12" width="5.22222222222222" style="2" customWidth="1"/>
-    <col min="13" max="13" width="39.017094017094" style="2" customWidth="1"/>
-    <col min="14" max="14" width="49.4358974358974" style="2" customWidth="1"/>
+    <col min="13" max="13" width="39.015873015873" style="2" customWidth="1"/>
+    <col min="14" max="14" width="49.4365079365079" style="2" customWidth="1"/>
     <col min="15" max="16384" width="9.11111111111111" style="2"/>
   </cols>
   <sheetData>
@@ -12018,10 +12171,10 @@
         <v>1000</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>19</v>
@@ -12033,7 +12186,7 @@
         <v>81</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="H2" s="2">
         <v>1</v>
@@ -12051,10 +12204,10 @@
         <v>19</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:16">
@@ -12062,10 +12215,10 @@
         <v>1001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>19</v>
@@ -12077,7 +12230,7 @@
         <v>82</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="H3" s="2">
         <v>1</v>
@@ -12095,10 +12248,10 @@
         <v>19</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:16">
@@ -12106,10 +12259,10 @@
         <v>1002</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>19</v>
@@ -12121,7 +12274,7 @@
         <v>83</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="H4" s="2">
         <v>1</v>
@@ -12139,10 +12292,10 @@
         <v>19</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:16">
@@ -12150,10 +12303,10 @@
         <v>1003</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>19</v>
@@ -12165,7 +12318,7 @@
         <v>84</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="H5" s="2">
         <v>1</v>
@@ -12183,10 +12336,10 @@
         <v>19</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:16">
@@ -12194,10 +12347,10 @@
         <v>1004</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>19</v>
@@ -12209,7 +12362,7 @@
         <v>85</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -12227,10 +12380,10 @@
         <v>19</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:16">
@@ -12238,10 +12391,10 @@
         <v>1005</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>19</v>
@@ -12253,7 +12406,7 @@
         <v>86</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -12271,10 +12424,10 @@
         <v>19</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:16">
@@ -12282,10 +12435,10 @@
         <v>1006</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>19</v>
@@ -12297,7 +12450,7 @@
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -12315,10 +12468,10 @@
         <v>19</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:16">
@@ -12326,10 +12479,10 @@
         <v>1007</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>19</v>
@@ -12341,7 +12494,7 @@
         <v>88</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -12359,10 +12512,10 @@
         <v>19</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" spans="1:16">
@@ -12370,10 +12523,10 @@
         <v>1008</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>19</v>
@@ -12385,7 +12538,7 @@
         <v>89</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -12403,10 +12556,10 @@
         <v>19</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" spans="1:16">
@@ -12414,10 +12567,10 @@
         <v>1009</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>19</v>
@@ -12429,7 +12582,7 @@
         <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -12447,21 +12600,21 @@
         <v>19</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
     </row>
     <row r="12" s="3" customFormat="1" spans="1:16">
       <c r="A12" s="3">
         <v>1010</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>222</v>
+      <c r="B12" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>19</v>
@@ -12473,7 +12626,7 @@
         <v>91</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="H12" s="3">
         <v>1</v>
@@ -12491,21 +12644,21 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" spans="1:16">
       <c r="A13" s="3">
         <v>1011</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>222</v>
+      <c r="B13" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>19</v>
@@ -12517,7 +12670,7 @@
         <v>92</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="H13" s="3">
         <v>1</v>
@@ -12535,21 +12688,21 @@
         <v>0</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" s="3" customFormat="1" spans="1:16">
       <c r="A14" s="3">
         <v>1012</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>222</v>
+      <c r="B14" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>19</v>
@@ -12561,7 +12714,7 @@
         <v>93</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="H14" s="3">
         <v>1</v>
@@ -12579,21 +12732,21 @@
         <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" spans="1:16">
       <c r="A15" s="2">
         <v>1013</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>475</v>
+      <c r="B15" s="7" t="s">
+        <v>483</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>19</v>
@@ -12605,7 +12758,7 @@
         <v>94</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -12623,21 +12776,21 @@
         <v>19</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:16">
       <c r="A16" s="2">
         <v>1014</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>478</v>
+      <c r="B16" s="7" t="s">
+        <v>486</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>19</v>
@@ -12649,7 +12802,7 @@
         <v>95</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -12667,21 +12820,21 @@
         <v>19</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" spans="1:14">
       <c r="A17" s="2">
         <v>1015</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>481</v>
+      <c r="B17" s="7" t="s">
+        <v>489</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>19</v>
@@ -12693,7 +12846,7 @@
         <v>96</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
@@ -12711,10 +12864,10 @@
         <v>19</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
@@ -12730,16 +12883,17 @@
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="9.11111111111111" style="2"/>
-    <col min="2" max="2" width="37.5299145299145" style="2" customWidth="1"/>
+    <col min="2" max="2" width="37.531746031746" style="2" customWidth="1"/>
     <col min="3" max="4" width="9.11111111111111" style="2"/>
-    <col min="5" max="5" width="20.8974358974359" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.957264957265" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.3931623931624" style="2" customWidth="1"/>
-    <col min="8" max="9" width="11.7435897435897" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.8968253968254" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.9603174603175" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.3968253968254" style="2" customWidth="1"/>
+    <col min="8" max="9" width="11.7460317460317" style="2" customWidth="1"/>
     <col min="10" max="12" width="9.11111111111111" style="2"/>
-    <col min="13" max="13" width="74.7863247863248" style="2" customWidth="1"/>
-    <col min="14" max="14" width="87.7692307692308" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9.11111111111111" style="2"/>
+    <col min="13" max="13" width="74.7857142857143" style="2" customWidth="1"/>
+    <col min="14" max="14" width="87.7698412698413" style="2" customWidth="1"/>
+    <col min="15" max="15" width="35.7619047619048" style="5" customWidth="1"/>
+    <col min="16" max="16384" width="9.11111111111111" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:16">
@@ -12785,19 +12939,19 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="90" spans="1:16">
+    <row r="2" s="2" customFormat="1" ht="162" spans="1:16">
       <c r="A2" s="2">
         <v>2000</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>17</v>
@@ -12805,14 +12959,12 @@
       <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>485</v>
-      </c>
+      <c r="E2" s="7"/>
       <c r="F2" s="2">
         <v>301</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H2" s="2">
         <v>1</v>
@@ -12830,10 +12982,13 @@
         <v>19</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>488</v>
+        <v>495</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:16">
@@ -12841,7 +12996,7 @@
         <v>2001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>17</v>
@@ -12856,7 +13011,7 @@
         <v>302</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H3" s="2">
         <v>1</v>
@@ -12874,18 +13029,19 @@
         <v>19</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>491</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="O3" s="5"/>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:16">
       <c r="A4" s="2">
         <v>2002</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>31</v>
@@ -12900,7 +13056,7 @@
         <v>303</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H4" s="2">
         <v>1</v>
@@ -12918,18 +13074,19 @@
         <v>19</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>494</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="O4" s="5"/>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:16">
       <c r="A5" s="2">
         <v>2003</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>31</v>
@@ -12944,7 +13101,7 @@
         <v>304</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H5" s="2">
         <v>1</v>
@@ -12962,18 +13119,19 @@
         <v>19</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>497</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="O5" s="5"/>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:16">
       <c r="A6" s="2">
         <v>2004</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>31</v>
@@ -12988,7 +13146,7 @@
         <v>305</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -13006,18 +13164,19 @@
         <v>19</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:16">
+        <v>508</v>
+      </c>
+      <c r="O6" s="5"/>
+    </row>
+    <row r="7" s="2" customFormat="1" ht="54" spans="1:16">
       <c r="A7" s="2">
         <v>2005</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>17</v>
@@ -13032,7 +13191,7 @@
         <v>306</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -13050,10 +13209,13 @@
         <v>19</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>503</v>
+        <v>511</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:16">
@@ -13061,7 +13223,7 @@
         <v>2006</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>17</v>
@@ -13076,7 +13238,7 @@
         <v>307</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -13094,18 +13256,19 @@
         <v>19</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>506</v>
-      </c>
+        <v>515</v>
+      </c>
+      <c r="O8" s="5"/>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:16">
       <c r="A9" s="2">
         <v>2007</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>17</v>
@@ -13120,7 +13283,7 @@
         <v>308</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -13138,18 +13301,19 @@
         <v>19</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>509</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="O9" s="5"/>
     </row>
     <row r="10" s="2" customFormat="1" spans="1:16">
       <c r="A10" s="2">
         <v>2008</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>31</v>
@@ -13164,7 +13328,7 @@
         <v>309</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -13182,18 +13346,19 @@
         <v>19</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>512</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="O10" s="5"/>
     </row>
     <row r="11" s="2" customFormat="1" spans="1:16">
       <c r="A11" s="2">
         <v>2009</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>513</v>
+      <c r="B11" s="9" t="s">
+        <v>522</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>31</v>
@@ -13208,7 +13373,7 @@
         <v>310</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -13226,18 +13391,19 @@
         <v>19</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>515</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="O11" s="5"/>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:16">
       <c r="A12" s="2">
         <v>2010</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>516</v>
+      <c r="B12" s="9" t="s">
+        <v>525</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>31</v>
@@ -13252,7 +13418,7 @@
         <v>311</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
@@ -13270,18 +13436,19 @@
         <v>19</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>518</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="O12" s="5"/>
     </row>
     <row r="13" s="2" customFormat="1" spans="1:16">
       <c r="A13" s="2">
         <v>2011</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>31</v>
@@ -13296,7 +13463,7 @@
         <v>312</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -13314,18 +13481,19 @@
         <v>19</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>521</v>
-      </c>
+        <v>530</v>
+      </c>
+      <c r="O13" s="5"/>
     </row>
     <row r="14" s="2" customFormat="1" spans="1:16">
       <c r="A14" s="2">
         <v>2012</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>522</v>
+      <c r="B14" s="9" t="s">
+        <v>531</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>31</v>
@@ -13340,7 +13508,7 @@
         <v>313</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -13358,18 +13526,19 @@
         <v>19</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>524</v>
-      </c>
+        <v>533</v>
+      </c>
+      <c r="O14" s="5"/>
     </row>
     <row r="15" s="2" customFormat="1" spans="1:16">
       <c r="A15" s="2">
         <v>2013</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>525</v>
+      <c r="B15" s="9" t="s">
+        <v>534</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>31</v>
@@ -13384,7 +13553,7 @@
         <v>314</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -13402,18 +13571,19 @@
         <v>19</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>527</v>
-      </c>
+        <v>536</v>
+      </c>
+      <c r="O15" s="5"/>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:16">
       <c r="A16" s="2">
         <v>2014</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>17</v>
@@ -13428,7 +13598,7 @@
         <v>315</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -13446,18 +13616,19 @@
         <v>19</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:14">
+        <v>539</v>
+      </c>
+      <c r="O16" s="5"/>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="1:15">
       <c r="A17" s="2">
         <v>2015</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>17</v>
@@ -13472,7 +13643,7 @@
         <v>316</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
@@ -13490,18 +13661,19 @@
         <v>19</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="1:14">
+        <v>542</v>
+      </c>
+      <c r="O17" s="5"/>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="1:15">
       <c r="A18" s="2">
         <v>2016</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>17</v>
@@ -13516,7 +13688,7 @@
         <v>317</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
@@ -13534,18 +13706,19 @@
         <v>19</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="19" s="3" customFormat="1" spans="1:14">
+        <v>545</v>
+      </c>
+      <c r="O18" s="5"/>
+    </row>
+    <row r="19" s="3" customFormat="1" spans="1:15">
       <c r="A19" s="3">
         <v>2017</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>17</v>
@@ -13560,7 +13733,7 @@
         <v>318</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H19" s="3">
         <v>1</v>
@@ -13574,22 +13747,23 @@
       <c r="K19" s="3">
         <v>0</v>
       </c>
-      <c r="L19" s="7">
+      <c r="L19" s="10">
         <v>0</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="1:14">
+        <v>225</v>
+      </c>
+      <c r="O19" s="11"/>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="1:15">
       <c r="A20" s="2">
         <v>2018</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>17</v>
@@ -13604,7 +13778,7 @@
         <v>319</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -13622,20 +13796,21 @@
         <v>19</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="1:14">
+        <v>548</v>
+      </c>
+      <c r="O20" s="5"/>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="1:15">
       <c r="A21" s="2">
         <v>2019</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="C21" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D21" s="2" t="s">
@@ -13648,7 +13823,7 @@
         <v>320</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -13666,20 +13841,21 @@
         <v>19</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" spans="1:14">
+        <v>551</v>
+      </c>
+      <c r="O21" s="5"/>
+    </row>
+    <row r="22" s="2" customFormat="1" spans="1:15">
       <c r="A22" s="2">
         <v>2020</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="C22" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="2" t="s">
@@ -13692,7 +13868,7 @@
         <v>321</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -13710,20 +13886,21 @@
         <v>19</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="23" s="3" customFormat="1" spans="1:14">
+        <v>554</v>
+      </c>
+      <c r="O22" s="5"/>
+    </row>
+    <row r="23" s="3" customFormat="1" spans="1:15">
       <c r="A23" s="3">
         <v>2021</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C23" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3" t="s">
@@ -13736,7 +13913,7 @@
         <v>322</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H23" s="3">
         <v>1</v>
@@ -13750,24 +13927,25 @@
       <c r="K23" s="3">
         <v>0</v>
       </c>
-      <c r="L23" s="7">
+      <c r="L23" s="10">
         <v>0</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" spans="1:14">
+        <v>225</v>
+      </c>
+      <c r="O23" s="11"/>
+    </row>
+    <row r="24" s="2" customFormat="1" spans="1:15">
       <c r="A24" s="2">
         <v>2022</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="C24" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D24" s="2" t="s">
@@ -13780,7 +13958,7 @@
         <v>323</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
@@ -13798,20 +13976,21 @@
         <v>19</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="1:14">
+        <v>557</v>
+      </c>
+      <c r="O24" s="5"/>
+    </row>
+    <row r="25" s="2" customFormat="1" spans="1:15">
       <c r="A25" s="2">
         <v>2023</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="C25" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="C25" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D25" s="2" t="s">
@@ -13824,7 +14003,7 @@
         <v>324</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
@@ -13842,20 +14021,21 @@
         <v>19</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" spans="1:14">
+        <v>560</v>
+      </c>
+      <c r="O25" s="5"/>
+    </row>
+    <row r="26" s="2" customFormat="1" spans="1:15">
       <c r="A26" s="2">
         <v>2024</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="C26" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D26" s="2" t="s">
@@ -13868,7 +14048,7 @@
         <v>325</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
@@ -13886,20 +14066,21 @@
         <v>19</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:14">
+        <v>563</v>
+      </c>
+      <c r="O26" s="5"/>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="1:15">
       <c r="A27" s="2">
         <v>2025</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="C27" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D27" s="2" t="s">
@@ -13912,7 +14093,7 @@
         <v>326</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
@@ -13930,20 +14111,21 @@
         <v>19</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" spans="1:14">
+        <v>566</v>
+      </c>
+      <c r="O27" s="5"/>
+    </row>
+    <row r="28" s="2" customFormat="1" spans="1:15">
       <c r="A28" s="2">
         <v>2026</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="C28" s="6" t="s">
+        <v>567</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D28" s="2" t="s">
@@ -13956,7 +14138,7 @@
         <v>327</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
@@ -13974,20 +14156,21 @@
         <v>19</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="1:14">
+        <v>569</v>
+      </c>
+      <c r="O28" s="5"/>
+    </row>
+    <row r="29" s="2" customFormat="1" spans="1:15">
       <c r="A29" s="2">
         <v>2027</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="C29" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="C29" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D29" s="2" t="s">
@@ -14000,7 +14183,7 @@
         <v>328</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
@@ -14018,20 +14201,21 @@
         <v>19</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:14">
+        <v>572</v>
+      </c>
+      <c r="O29" s="5"/>
+    </row>
+    <row r="30" s="2" customFormat="1" spans="1:15">
       <c r="A30" s="2">
         <v>2028</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="C30" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="C30" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D30" s="2" t="s">
@@ -14044,7 +14228,7 @@
         <v>329</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
@@ -14062,20 +14246,21 @@
         <v>19</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>565</v>
+        <v>574</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="1:14">
+        <v>575</v>
+      </c>
+      <c r="O30" s="5"/>
+    </row>
+    <row r="31" s="2" customFormat="1" spans="1:15">
       <c r="A31" s="2">
         <v>2029</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="C31" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="C31" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D31" s="2" t="s">
@@ -14088,7 +14273,7 @@
         <v>330</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
@@ -14106,20 +14291,21 @@
         <v>19</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="1:14">
+        <v>578</v>
+      </c>
+      <c r="O31" s="5"/>
+    </row>
+    <row r="32" s="2" customFormat="1" spans="1:15">
       <c r="A32" s="2">
         <v>2030</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="C32" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D32" s="2" t="s">
@@ -14132,7 +14318,7 @@
         <v>331</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H32" s="2">
         <v>1</v>
@@ -14150,20 +14336,21 @@
         <v>19</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" spans="1:14">
+        <v>581</v>
+      </c>
+      <c r="O32" s="5"/>
+    </row>
+    <row r="33" s="2" customFormat="1" spans="1:15">
       <c r="A33" s="2">
         <v>2031</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="C33" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="C33" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D33" s="2" t="s">
@@ -14176,7 +14363,7 @@
         <v>332</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H33" s="2">
         <v>1</v>
@@ -14194,20 +14381,21 @@
         <v>19</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" spans="1:14">
+        <v>584</v>
+      </c>
+      <c r="O33" s="5"/>
+    </row>
+    <row r="34" s="2" customFormat="1" spans="1:15">
       <c r="A34" s="2">
         <v>2032</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="C34" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="C34" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D34" s="2" t="s">
@@ -14220,7 +14408,7 @@
         <v>333</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
@@ -14238,20 +14426,21 @@
         <v>19</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" spans="1:14">
+        <v>587</v>
+      </c>
+      <c r="O34" s="5"/>
+    </row>
+    <row r="35" s="2" customFormat="1" spans="1:15">
       <c r="A35" s="2">
         <v>2033</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="C35" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="C35" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D35" s="2" t="s">
@@ -14264,7 +14453,7 @@
         <v>334</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H35" s="2">
         <v>1</v>
@@ -14282,20 +14471,21 @@
         <v>19</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" spans="1:14">
+        <v>590</v>
+      </c>
+      <c r="O35" s="5"/>
+    </row>
+    <row r="36" s="2" customFormat="1" spans="1:15">
       <c r="A36" s="2">
         <v>2034</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="C36" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D36" s="2" t="s">
@@ -14308,7 +14498,7 @@
         <v>335</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H36" s="2">
         <v>1</v>
@@ -14326,20 +14516,21 @@
         <v>19</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" spans="1:14">
+        <v>593</v>
+      </c>
+      <c r="O36" s="5"/>
+    </row>
+    <row r="37" s="2" customFormat="1" spans="1:15">
       <c r="A37" s="2">
         <v>2035</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="C37" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="C37" s="9" t="s">
         <v>31</v>
       </c>
       <c r="D37" s="2" t="s">
@@ -14352,7 +14543,7 @@
         <v>336</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H37" s="2">
         <v>1</v>
@@ -14370,20 +14561,21 @@
         <v>19</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="38" s="3" customFormat="1" spans="1:14">
+        <v>596</v>
+      </c>
+      <c r="O37" s="5"/>
+    </row>
+    <row r="38" s="3" customFormat="1" spans="1:15">
       <c r="A38" s="3">
         <v>2036</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C38" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C38" s="10" t="s">
         <v>31</v>
       </c>
       <c r="D38" s="3" t="s">
@@ -14396,7 +14588,7 @@
         <v>337</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H38" s="3">
         <v>1</v>
@@ -14410,24 +14602,25 @@
       <c r="K38" s="3">
         <v>0</v>
       </c>
-      <c r="L38" s="7">
+      <c r="L38" s="10">
         <v>0</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="39" s="3" customFormat="1" spans="1:14">
+        <v>225</v>
+      </c>
+      <c r="O38" s="11"/>
+    </row>
+    <row r="39" s="3" customFormat="1" spans="1:15">
       <c r="A39" s="3">
         <v>2037</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C39" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C39" s="10" t="s">
         <v>31</v>
       </c>
       <c r="D39" s="3" t="s">
@@ -14440,7 +14633,7 @@
         <v>338</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H39" s="3">
         <v>1</v>
@@ -14454,24 +14647,25 @@
       <c r="K39" s="3">
         <v>0</v>
       </c>
-      <c r="L39" s="7">
+      <c r="L39" s="10">
         <v>0</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="40" s="3" customFormat="1" spans="1:14">
+        <v>225</v>
+      </c>
+      <c r="O39" s="11"/>
+    </row>
+    <row r="40" s="3" customFormat="1" spans="1:15">
       <c r="A40" s="3">
         <v>2038</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C40" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C40" s="10" t="s">
         <v>31</v>
       </c>
       <c r="D40" s="3" t="s">
@@ -14484,7 +14678,7 @@
         <v>339</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H40" s="3">
         <v>1</v>
@@ -14498,24 +14692,25 @@
       <c r="K40" s="3">
         <v>0</v>
       </c>
-      <c r="L40" s="7">
+      <c r="L40" s="10">
         <v>0</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="41" s="2" customFormat="1" spans="1:14">
+        <v>225</v>
+      </c>
+      <c r="O40" s="11"/>
+    </row>
+    <row r="41" s="2" customFormat="1" spans="1:15">
       <c r="A41" s="2">
         <v>2039</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="C41" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="C41" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D41" s="2" t="s">
@@ -14528,7 +14723,7 @@
         <v>340</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H41" s="2">
         <v>1</v>
@@ -14546,20 +14741,21 @@
         <v>19</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="42" s="2" customFormat="1" spans="1:14">
+        <v>599</v>
+      </c>
+      <c r="O41" s="5"/>
+    </row>
+    <row r="42" s="2" customFormat="1" spans="1:15">
       <c r="A42" s="2">
         <v>2040</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="C42" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="C42" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D42" s="2" t="s">
@@ -14572,7 +14768,7 @@
         <v>341</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H42" s="2">
         <v>1</v>
@@ -14590,24 +14786,25 @@
         <v>19</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" spans="1:14">
+        <v>602</v>
+      </c>
+      <c r="O42" s="5"/>
+    </row>
+    <row r="43" s="2" customFormat="1" spans="1:15">
       <c r="A43" s="2">
         <v>2041</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="C43" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="C43" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>19</v>
@@ -14616,7 +14813,7 @@
         <v>342</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H43" s="2">
         <v>1</v>
@@ -14634,20 +14831,21 @@
         <v>19</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>595</v>
+        <v>604</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="44" s="2" customFormat="1" spans="1:14">
+        <v>605</v>
+      </c>
+      <c r="O43" s="5"/>
+    </row>
+    <row r="44" s="2" customFormat="1" spans="1:15">
       <c r="A44" s="2">
         <v>2042</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="C44" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="C44" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D44" s="2" t="s">
@@ -14660,7 +14858,7 @@
         <v>343</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H44" s="2">
         <v>1</v>
@@ -14678,11 +14876,12 @@
         <v>19</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>598</v>
+        <v>607</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>599</v>
-      </c>
+        <v>608</v>
+      </c>
+      <c r="O44" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14697,14 +14896,14 @@
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="9.11111111111111" style="2"/>
-    <col min="2" max="2" width="19.5213675213675" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.5238095238095" style="2" customWidth="1"/>
     <col min="3" max="5" width="9.11111111111111" style="2"/>
-    <col min="6" max="6" width="10.957264957265" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.3931623931624" style="2" customWidth="1"/>
-    <col min="8" max="9" width="11.7435897435897" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.9603174603175" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.3968253968254" style="2" customWidth="1"/>
+    <col min="8" max="9" width="11.7460317460317" style="2" customWidth="1"/>
     <col min="10" max="12" width="9.11111111111111" style="2"/>
-    <col min="13" max="13" width="41.2307692307692" style="2" customWidth="1"/>
-    <col min="14" max="14" width="50.3589743589744" style="2" customWidth="1"/>
+    <col min="13" max="13" width="41.2301587301587" style="2" customWidth="1"/>
+    <col min="14" max="14" width="50.3571428571429" style="2" customWidth="1"/>
     <col min="15" max="16384" width="9.11111111111111" style="2"/>
   </cols>
   <sheetData>
@@ -14763,10 +14962,10 @@
         <v>3000</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>19</v>
@@ -14778,7 +14977,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="H2" s="2">
         <v>1</v>
@@ -14796,10 +14995,10 @@
         <v>19</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>603</v>
+        <v>612</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:16">
@@ -14807,10 +15006,10 @@
         <v>3001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>604</v>
+        <v>613</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>19</v>
@@ -14822,7 +15021,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="H3" s="2">
         <v>1</v>
@@ -14840,10 +15039,10 @@
         <v>19</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:16">
@@ -14851,10 +15050,10 @@
         <v>3002</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>19</v>
@@ -14866,7 +15065,7 @@
         <v>3</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="H4" s="2">
         <v>1</v>
@@ -14884,10 +15083,10 @@
         <v>19</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:16">
@@ -14895,10 +15094,10 @@
         <v>3003</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>19</v>
@@ -14910,7 +15109,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="H5" s="2">
         <v>1</v>
@@ -14928,10 +15127,10 @@
         <v>19</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:16">
@@ -14939,10 +15138,10 @@
         <v>3004</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>19</v>
@@ -14954,7 +15153,7 @@
         <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -14972,10 +15171,10 @@
         <v>19</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:16">
@@ -14983,10 +15182,10 @@
         <v>3005</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>19</v>
@@ -14998,7 +15197,7 @@
         <v>6</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -15016,10 +15215,10 @@
         <v>19</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:16">
@@ -15027,10 +15226,10 @@
         <v>3006</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>619</v>
+        <v>628</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>19</v>
@@ -15042,7 +15241,7 @@
         <v>7</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -15060,10 +15259,10 @@
         <v>19</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:16">
@@ -15071,10 +15270,10 @@
         <v>3007</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>19</v>
@@ -15086,7 +15285,7 @@
         <v>8</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -15104,10 +15303,10 @@
         <v>19</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
     </row>
     <row r="10" s="3" customFormat="1" spans="1:16">
@@ -15115,10 +15314,10 @@
         <v>3008</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>19</v>
@@ -15130,7 +15329,7 @@
         <v>9</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="H10" s="3">
         <v>1</v>
@@ -15148,10 +15347,10 @@
         <v>0</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" s="3" customFormat="1" spans="1:16">
@@ -15159,10 +15358,10 @@
         <v>3009</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>19</v>
@@ -15174,7 +15373,7 @@
         <v>10</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="H11" s="3">
         <v>1</v>
@@ -15192,10 +15391,10 @@
         <v>0</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12" s="3" customFormat="1" spans="1:16">
@@ -15203,10 +15402,10 @@
         <v>3010</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>19</v>
@@ -15218,7 +15417,7 @@
         <v>11</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="H12" s="3">
         <v>1</v>
@@ -15236,10 +15435,10 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" spans="1:16">
@@ -15247,10 +15446,10 @@
         <v>3011</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>19</v>
@@ -15262,7 +15461,7 @@
         <v>12</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="H13" s="3">
         <v>1</v>
@@ -15280,10 +15479,10 @@
         <v>0</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" s="3" customFormat="1" spans="1:16">
@@ -15291,10 +15490,10 @@
         <v>3012</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>19</v>
@@ -15306,7 +15505,7 @@
         <v>13</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="H14" s="3">
         <v>1</v>
@@ -15324,10 +15523,10 @@
         <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" spans="1:16">
@@ -15335,10 +15534,10 @@
         <v>3013</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>19</v>
@@ -15350,7 +15549,7 @@
         <v>14</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="H15" s="3">
         <v>1</v>
@@ -15368,10 +15567,10 @@
         <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16" s="3" customFormat="1" spans="1:16">
@@ -15379,10 +15578,10 @@
         <v>3014</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>19</v>
@@ -15394,7 +15593,7 @@
         <v>15</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="H16" s="3">
         <v>1</v>
@@ -15412,10 +15611,10 @@
         <v>0</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17" s="3" customFormat="1" spans="1:14">
@@ -15423,10 +15622,10 @@
         <v>3015</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>19</v>
@@ -15438,7 +15637,7 @@
         <v>16</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="H17" s="3">
         <v>1</v>
@@ -15456,10 +15655,10 @@
         <v>0</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>

--- a/config/PCS_125_英博.xlsx
+++ b/config/PCS_125_英博.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18519" windowHeight="11218"/>
+    <workbookView windowWidth="18519" windowHeight="11218" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="遥测" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2680" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2690" uniqueCount="644">
   <si>
     <t>序号</t>
   </si>
@@ -1509,6 +1509,9 @@
     <t>{"en":"Shutdown status"}</t>
   </si>
   <si>
+    <t>1 停机|stop</t>
+  </si>
+  <si>
     <t>待机状态</t>
   </si>
   <si>
@@ -1518,6 +1521,9 @@
     <t>{"en":"standby mode"}</t>
   </si>
   <si>
+    <t>1 待机|standBy</t>
+  </si>
+  <si>
     <t>运行状态</t>
   </si>
   <si>
@@ -1527,6 +1533,9 @@
     <t>{"en":"Operating status"}</t>
   </si>
   <si>
+    <t>1 运行|running</t>
+  </si>
+  <si>
     <t>总故障状态</t>
   </si>
   <si>
@@ -1536,6 +1545,9 @@
     <t>{"en":"Overall fault status"}</t>
   </si>
   <si>
+    <t>1 故障|fault</t>
+  </si>
+  <si>
     <t>总报警状态</t>
   </si>
   <si>
@@ -1545,6 +1557,9 @@
     <t>{"en":"Overall alarm status"}</t>
   </si>
   <si>
+    <t>1 报警|warn</t>
+  </si>
+  <si>
     <t>远程/就地状态</t>
   </si>
   <si>
@@ -1554,6 +1569,10 @@
     <t>{"en":"Remote/Local Status"}</t>
   </si>
   <si>
+    <t>0 就地|nearby
+1 远程|remote</t>
+  </si>
+  <si>
     <t>急停输入状态</t>
   </si>
   <si>
@@ -1563,6 +1582,9 @@
     <t>{"en":"Emergency stop input status"}</t>
   </si>
   <si>
+    <t>1 急停有效|emergency</t>
+  </si>
+  <si>
     <t>并网状态</t>
   </si>
   <si>
@@ -1572,6 +1594,9 @@
     <t>{"en":"grid-connected state"}</t>
   </si>
   <si>
+    <t>1 并网|grid-tie</t>
+  </si>
+  <si>
     <t>VF 离网状态</t>
   </si>
   <si>
@@ -1581,6 +1606,9 @@
     <t>{"en":"VF off grid status"}</t>
   </si>
   <si>
+    <t>1 离网|off-grid</t>
+  </si>
+  <si>
     <t>过载降容</t>
   </si>
   <si>
@@ -1588,6 +1616,9 @@
   </si>
   <si>
     <t>{"en":"Overload and Capacity Reduction"}</t>
+  </si>
+  <si>
+    <t>1 过载发生|overload</t>
   </si>
   <si>
     <t>BMS 干接点输入状态</t>
@@ -2688,7 +2719,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2722,6 +2753,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -12113,7 +12147,8 @@
     <col min="12" max="12" width="5.22222222222222" style="2" customWidth="1"/>
     <col min="13" max="13" width="39.015873015873" style="2" customWidth="1"/>
     <col min="14" max="14" width="49.4365079365079" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9.11111111111111" style="2"/>
+    <col min="15" max="15" width="28.7460317460317" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9.11111111111111" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:16">
@@ -12209,13 +12244,16 @@
       <c r="N2" s="2" t="s">
         <v>455</v>
       </c>
+      <c r="O2" s="12" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:16">
       <c r="A3" s="2">
         <v>1001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>452</v>
@@ -12248,10 +12286,13 @@
         <v>19</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
+      </c>
+      <c r="O3" s="12" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:16">
@@ -12259,7 +12300,7 @@
         <v>1002</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>452</v>
@@ -12292,10 +12333,13 @@
         <v>19</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:16">
@@ -12303,7 +12347,7 @@
         <v>1003</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>452</v>
@@ -12336,10 +12380,13 @@
         <v>19</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>464</v>
+        <v>467</v>
+      </c>
+      <c r="O5" s="12" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:16">
@@ -12347,7 +12394,7 @@
         <v>1004</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>452</v>
@@ -12380,18 +12427,21 @@
         <v>19</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:16">
+        <v>471</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" ht="36" spans="1:16">
       <c r="A7" s="2">
         <v>1005</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>452</v>
@@ -12424,10 +12474,13 @@
         <v>19</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>470</v>
+        <v>475</v>
+      </c>
+      <c r="O7" s="12" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:16">
@@ -12435,7 +12488,7 @@
         <v>1006</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>452</v>
@@ -12468,10 +12521,13 @@
         <v>19</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>473</v>
+        <v>479</v>
+      </c>
+      <c r="O8" s="12" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:16">
@@ -12479,7 +12535,7 @@
         <v>1007</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>452</v>
@@ -12512,10 +12568,13 @@
         <v>19</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>476</v>
+        <v>483</v>
+      </c>
+      <c r="O9" s="12" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" spans="1:16">
@@ -12523,7 +12582,7 @@
         <v>1008</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>452</v>
@@ -12556,10 +12615,13 @@
         <v>19</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>479</v>
+        <v>487</v>
+      </c>
+      <c r="O10" s="12" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" spans="1:16">
@@ -12567,7 +12629,7 @@
         <v>1009</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>452</v>
@@ -12600,17 +12662,20 @@
         <v>19</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>482</v>
+        <v>491</v>
+      </c>
+      <c r="O11" s="12" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="12" s="3" customFormat="1" spans="1:16">
       <c r="A12" s="3">
         <v>1010</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="13" t="s">
         <v>223</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -12654,7 +12719,7 @@
       <c r="A13" s="3">
         <v>1011</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="13" t="s">
         <v>223</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -12698,7 +12763,7 @@
       <c r="A14" s="3">
         <v>1012</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="13" t="s">
         <v>223</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -12743,7 +12808,7 @@
         <v>1013</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>452</v>
@@ -12776,10 +12841,10 @@
         <v>19</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:16">
@@ -12787,7 +12852,7 @@
         <v>1014</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>452</v>
@@ -12820,10 +12885,10 @@
         <v>19</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" spans="1:14">
@@ -12831,7 +12896,7 @@
         <v>1015</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>452</v>
@@ -12864,10 +12929,10 @@
         <v>19</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
     </row>
   </sheetData>
@@ -12946,12 +13011,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="162" spans="1:16">
+    <row r="2" s="2" customFormat="1" ht="90" spans="1:16">
       <c r="A2" s="2">
         <v>2000</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>17</v>
@@ -12964,7 +13029,7 @@
         <v>301</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H2" s="2">
         <v>1</v>
@@ -12982,13 +13047,13 @@
         <v>19</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:16">
@@ -12996,7 +13061,7 @@
         <v>2001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>17</v>
@@ -13011,7 +13076,7 @@
         <v>302</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H3" s="2">
         <v>1</v>
@@ -13029,10 +13094,10 @@
         <v>19</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="O3" s="5"/>
     </row>
@@ -13041,7 +13106,7 @@
         <v>2002</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>31</v>
@@ -13056,7 +13121,7 @@
         <v>303</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H4" s="2">
         <v>1</v>
@@ -13074,10 +13139,10 @@
         <v>19</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="O4" s="5"/>
     </row>
@@ -13086,7 +13151,7 @@
         <v>2003</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>31</v>
@@ -13101,7 +13166,7 @@
         <v>304</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H5" s="2">
         <v>1</v>
@@ -13119,10 +13184,10 @@
         <v>19</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="O5" s="5"/>
     </row>
@@ -13131,7 +13196,7 @@
         <v>2004</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>31</v>
@@ -13146,7 +13211,7 @@
         <v>305</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -13164,10 +13229,10 @@
         <v>19</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="O6" s="5"/>
     </row>
@@ -13176,7 +13241,7 @@
         <v>2005</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>17</v>
@@ -13191,7 +13256,7 @@
         <v>306</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -13209,13 +13274,13 @@
         <v>19</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:16">
@@ -13223,7 +13288,7 @@
         <v>2006</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>17</v>
@@ -13238,7 +13303,7 @@
         <v>307</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -13256,10 +13321,10 @@
         <v>19</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="O8" s="5"/>
     </row>
@@ -13268,7 +13333,7 @@
         <v>2007</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>17</v>
@@ -13283,7 +13348,7 @@
         <v>308</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -13301,10 +13366,10 @@
         <v>19</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="O9" s="5"/>
     </row>
@@ -13313,7 +13378,7 @@
         <v>2008</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>31</v>
@@ -13328,7 +13393,7 @@
         <v>309</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -13346,10 +13411,10 @@
         <v>19</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="O10" s="5"/>
     </row>
@@ -13358,7 +13423,7 @@
         <v>2009</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>31</v>
@@ -13373,7 +13438,7 @@
         <v>310</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -13391,10 +13456,10 @@
         <v>19</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="O11" s="5"/>
     </row>
@@ -13403,7 +13468,7 @@
         <v>2010</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>31</v>
@@ -13418,7 +13483,7 @@
         <v>311</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
@@ -13436,10 +13501,10 @@
         <v>19</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="O12" s="5"/>
     </row>
@@ -13448,7 +13513,7 @@
         <v>2011</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>31</v>
@@ -13463,7 +13528,7 @@
         <v>312</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -13481,10 +13546,10 @@
         <v>19</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="O13" s="5"/>
     </row>
@@ -13493,7 +13558,7 @@
         <v>2012</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>31</v>
@@ -13508,7 +13573,7 @@
         <v>313</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -13526,10 +13591,10 @@
         <v>19</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="O14" s="5"/>
     </row>
@@ -13538,7 +13603,7 @@
         <v>2013</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>31</v>
@@ -13553,7 +13618,7 @@
         <v>314</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -13571,10 +13636,10 @@
         <v>19</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="O15" s="5"/>
     </row>
@@ -13583,7 +13648,7 @@
         <v>2014</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>17</v>
@@ -13598,7 +13663,7 @@
         <v>315</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -13616,10 +13681,10 @@
         <v>19</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="O16" s="5"/>
     </row>
@@ -13628,7 +13693,7 @@
         <v>2015</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>17</v>
@@ -13643,7 +13708,7 @@
         <v>316</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
@@ -13661,10 +13726,10 @@
         <v>19</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>541</v>
+        <v>551</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="O17" s="5"/>
     </row>
@@ -13673,7 +13738,7 @@
         <v>2016</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>543</v>
+        <v>553</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>17</v>
@@ -13688,7 +13753,7 @@
         <v>317</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
@@ -13706,10 +13771,10 @@
         <v>19</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>544</v>
+        <v>554</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>545</v>
+        <v>555</v>
       </c>
       <c r="O18" s="5"/>
     </row>
@@ -13733,7 +13798,7 @@
         <v>318</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H19" s="3">
         <v>1</v>
@@ -13763,7 +13828,7 @@
         <v>2018</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>17</v>
@@ -13778,7 +13843,7 @@
         <v>319</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -13796,10 +13861,10 @@
         <v>19</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="O20" s="5"/>
     </row>
@@ -13808,7 +13873,7 @@
         <v>2019</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>17</v>
@@ -13823,7 +13888,7 @@
         <v>320</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -13841,10 +13906,10 @@
         <v>19</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>551</v>
+        <v>561</v>
       </c>
       <c r="O21" s="5"/>
     </row>
@@ -13853,7 +13918,7 @@
         <v>2020</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>17</v>
@@ -13868,7 +13933,7 @@
         <v>321</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -13886,10 +13951,10 @@
         <v>19</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>554</v>
+        <v>564</v>
       </c>
       <c r="O22" s="5"/>
     </row>
@@ -13913,7 +13978,7 @@
         <v>322</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H23" s="3">
         <v>1</v>
@@ -13943,7 +14008,7 @@
         <v>2022</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>555</v>
+        <v>565</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>17</v>
@@ -13958,7 +14023,7 @@
         <v>323</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
@@ -13976,10 +14041,10 @@
         <v>19</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>557</v>
+        <v>567</v>
       </c>
       <c r="O24" s="5"/>
     </row>
@@ -13988,7 +14053,7 @@
         <v>2023</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>558</v>
+        <v>568</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>17</v>
@@ -14003,7 +14068,7 @@
         <v>324</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
@@ -14021,10 +14086,10 @@
         <v>19</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="O25" s="5"/>
     </row>
@@ -14033,7 +14098,7 @@
         <v>2024</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>561</v>
+        <v>571</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>17</v>
@@ -14048,7 +14113,7 @@
         <v>325</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
@@ -14066,10 +14131,10 @@
         <v>19</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>562</v>
+        <v>572</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>563</v>
+        <v>573</v>
       </c>
       <c r="O26" s="5"/>
     </row>
@@ -14078,7 +14143,7 @@
         <v>2025</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>17</v>
@@ -14093,7 +14158,7 @@
         <v>326</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
@@ -14111,10 +14176,10 @@
         <v>19</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="O27" s="5"/>
     </row>
@@ -14123,7 +14188,7 @@
         <v>2026</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>17</v>
@@ -14138,7 +14203,7 @@
         <v>327</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
@@ -14156,10 +14221,10 @@
         <v>19</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>569</v>
+        <v>579</v>
       </c>
       <c r="O28" s="5"/>
     </row>
@@ -14168,7 +14233,7 @@
         <v>2027</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>17</v>
@@ -14183,7 +14248,7 @@
         <v>328</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
@@ -14201,10 +14266,10 @@
         <v>19</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>571</v>
+        <v>581</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="O29" s="5"/>
     </row>
@@ -14213,7 +14278,7 @@
         <v>2028</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>573</v>
+        <v>583</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>17</v>
@@ -14228,7 +14293,7 @@
         <v>329</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
@@ -14246,10 +14311,10 @@
         <v>19</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="O30" s="5"/>
     </row>
@@ -14258,7 +14323,7 @@
         <v>2029</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>17</v>
@@ -14273,7 +14338,7 @@
         <v>330</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
@@ -14291,10 +14356,10 @@
         <v>19</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="O31" s="5"/>
     </row>
@@ -14303,7 +14368,7 @@
         <v>2030</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>17</v>
@@ -14318,7 +14383,7 @@
         <v>331</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H32" s="2">
         <v>1</v>
@@ -14336,10 +14401,10 @@
         <v>19</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="O32" s="5"/>
     </row>
@@ -14348,7 +14413,7 @@
         <v>2031</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>17</v>
@@ -14363,7 +14428,7 @@
         <v>332</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H33" s="2">
         <v>1</v>
@@ -14381,10 +14446,10 @@
         <v>19</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>583</v>
+        <v>593</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>584</v>
+        <v>594</v>
       </c>
       <c r="O33" s="5"/>
     </row>
@@ -14393,7 +14458,7 @@
         <v>2032</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>17</v>
@@ -14408,7 +14473,7 @@
         <v>333</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
@@ -14426,10 +14491,10 @@
         <v>19</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="O34" s="5"/>
     </row>
@@ -14438,7 +14503,7 @@
         <v>2033</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>17</v>
@@ -14453,7 +14518,7 @@
         <v>334</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H35" s="2">
         <v>1</v>
@@ -14471,10 +14536,10 @@
         <v>19</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="O35" s="5"/>
     </row>
@@ -14483,7 +14548,7 @@
         <v>2034</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>17</v>
@@ -14498,7 +14563,7 @@
         <v>335</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H36" s="2">
         <v>1</v>
@@ -14516,10 +14581,10 @@
         <v>19</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>592</v>
+        <v>602</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="O36" s="5"/>
     </row>
@@ -14528,7 +14593,7 @@
         <v>2035</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>594</v>
+        <v>604</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>31</v>
@@ -14543,7 +14608,7 @@
         <v>336</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H37" s="2">
         <v>1</v>
@@ -14561,10 +14626,10 @@
         <v>19</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>595</v>
+        <v>605</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>596</v>
+        <v>606</v>
       </c>
       <c r="O37" s="5"/>
     </row>
@@ -14588,7 +14653,7 @@
         <v>337</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H38" s="3">
         <v>1</v>
@@ -14633,7 +14698,7 @@
         <v>338</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H39" s="3">
         <v>1</v>
@@ -14678,7 +14743,7 @@
         <v>339</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H40" s="3">
         <v>1</v>
@@ -14708,7 +14773,7 @@
         <v>2039</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>597</v>
+        <v>607</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>17</v>
@@ -14723,7 +14788,7 @@
         <v>340</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H41" s="2">
         <v>1</v>
@@ -14741,10 +14806,10 @@
         <v>19</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>598</v>
+        <v>608</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>599</v>
+        <v>609</v>
       </c>
       <c r="O41" s="5"/>
     </row>
@@ -14753,7 +14818,7 @@
         <v>2040</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>17</v>
@@ -14768,7 +14833,7 @@
         <v>341</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H42" s="2">
         <v>1</v>
@@ -14786,10 +14851,10 @@
         <v>19</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>601</v>
+        <v>611</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>602</v>
+        <v>612</v>
       </c>
       <c r="O42" s="5"/>
     </row>
@@ -14798,7 +14863,7 @@
         <v>2041</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>603</v>
+        <v>613</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>17</v>
@@ -14813,7 +14878,7 @@
         <v>342</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H43" s="2">
         <v>1</v>
@@ -14831,10 +14896,10 @@
         <v>19</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>604</v>
+        <v>614</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
       <c r="O43" s="5"/>
     </row>
@@ -14843,7 +14908,7 @@
         <v>2042</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>606</v>
+        <v>616</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>17</v>
@@ -14858,7 +14923,7 @@
         <v>343</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H44" s="2">
         <v>1</v>
@@ -14876,10 +14941,10 @@
         <v>19</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>607</v>
+        <v>617</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="O44" s="5"/>
     </row>
@@ -14962,7 +15027,7 @@
         <v>3000</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>609</v>
+        <v>619</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>452</v>
@@ -14977,7 +15042,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="H2" s="2">
         <v>1</v>
@@ -14995,10 +15060,10 @@
         <v>19</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>611</v>
+        <v>621</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>612</v>
+        <v>622</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:16">
@@ -15006,7 +15071,7 @@
         <v>3001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>452</v>
@@ -15021,7 +15086,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="H3" s="2">
         <v>1</v>
@@ -15039,10 +15104,10 @@
         <v>19</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>614</v>
+        <v>624</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>615</v>
+        <v>625</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:16">
@@ -15050,7 +15115,7 @@
         <v>3002</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>616</v>
+        <v>626</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>452</v>
@@ -15065,7 +15130,7 @@
         <v>3</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="H4" s="2">
         <v>1</v>
@@ -15083,10 +15148,10 @@
         <v>19</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>617</v>
+        <v>627</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>618</v>
+        <v>628</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:16">
@@ -15094,7 +15159,7 @@
         <v>3003</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>619</v>
+        <v>629</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>452</v>
@@ -15109,7 +15174,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="H5" s="2">
         <v>1</v>
@@ -15127,10 +15192,10 @@
         <v>19</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>621</v>
+        <v>631</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:16">
@@ -15138,7 +15203,7 @@
         <v>3004</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>622</v>
+        <v>632</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>452</v>
@@ -15153,7 +15218,7 @@
         <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -15171,10 +15236,10 @@
         <v>19</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>623</v>
+        <v>633</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>624</v>
+        <v>634</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:16">
@@ -15182,7 +15247,7 @@
         <v>3005</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>625</v>
+        <v>635</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>452</v>
@@ -15197,7 +15262,7 @@
         <v>6</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -15215,10 +15280,10 @@
         <v>19</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>626</v>
+        <v>636</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>627</v>
+        <v>637</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:16">
@@ -15226,7 +15291,7 @@
         <v>3006</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>628</v>
+        <v>638</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>452</v>
@@ -15241,7 +15306,7 @@
         <v>7</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -15259,10 +15324,10 @@
         <v>19</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>629</v>
+        <v>639</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>630</v>
+        <v>640</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:16">
@@ -15270,7 +15335,7 @@
         <v>3007</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>452</v>
@@ -15285,7 +15350,7 @@
         <v>8</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -15303,10 +15368,10 @@
         <v>19</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>632</v>
+        <v>642</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>633</v>
+        <v>643</v>
       </c>
     </row>
     <row r="10" s="3" customFormat="1" spans="1:16">
@@ -15329,7 +15394,7 @@
         <v>9</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="H10" s="3">
         <v>1</v>
@@ -15373,7 +15438,7 @@
         <v>10</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="H11" s="3">
         <v>1</v>
@@ -15417,7 +15482,7 @@
         <v>11</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="H12" s="3">
         <v>1</v>
@@ -15461,7 +15526,7 @@
         <v>12</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="H13" s="3">
         <v>1</v>
@@ -15505,7 +15570,7 @@
         <v>13</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="H14" s="3">
         <v>1</v>
@@ -15549,7 +15614,7 @@
         <v>14</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="H15" s="3">
         <v>1</v>
@@ -15593,7 +15658,7 @@
         <v>15</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="H16" s="3">
         <v>1</v>
@@ -15637,7 +15702,7 @@
         <v>16</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="H17" s="3">
         <v>1</v>

--- a/config/PCS_125_英博.xlsx
+++ b/config/PCS_125_英博.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18519" windowHeight="11218" activeTab="1"/>
+    <workbookView windowWidth="18569" windowHeight="11268"/>
   </bookViews>
   <sheets>
     <sheet name="遥测" sheetId="1" r:id="rId1"/>

--- a/config/PCS_125_英博.xlsx
+++ b/config/PCS_125_英博.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18569" windowHeight="11268"/>
+    <workbookView windowWidth="22010" windowHeight="12332"/>
   </bookViews>
   <sheets>
     <sheet name="遥测" sheetId="1" r:id="rId1"/>

--- a/config/PCS_125_英博.xlsx
+++ b/config/PCS_125_英博.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332"/>
+    <workbookView windowWidth="18519" windowHeight="11218" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="遥测" sheetId="1" r:id="rId1"/>
@@ -1509,7 +1509,8 @@
     <t>{"en":"Shutdown status"}</t>
   </si>
   <si>
-    <t>1 停机|stop</t>
+    <t>0 待机|standBy
+1 停机|stop</t>
   </si>
   <si>
     <t>待机状态</t>
@@ -1521,7 +1522,8 @@
     <t>{"en":"standby mode"}</t>
   </si>
   <si>
-    <t>1 待机|standBy</t>
+    <t>0 停机|stop
+1 待机|standBy</t>
   </si>
   <si>
     <t>运行状态</t>
@@ -1533,7 +1535,8 @@
     <t>{"en":"Operating status"}</t>
   </si>
   <si>
-    <t>1 运行|running</t>
+    <t>0 停止|stop
+1 运行|running</t>
   </si>
   <si>
     <t>总故障状态</t>
@@ -1545,7 +1548,8 @@
     <t>{"en":"Overall fault status"}</t>
   </si>
   <si>
-    <t>1 故障|fault</t>
+    <t>0 正常|normal
+1 故障|fault</t>
   </si>
   <si>
     <t>总报警状态</t>
@@ -1557,7 +1561,8 @@
     <t>{"en":"Overall alarm status"}</t>
   </si>
   <si>
-    <t>1 报警|warn</t>
+    <t>0 正常|normal
+1 报警|warn</t>
   </si>
   <si>
     <t>远程/就地状态</t>
@@ -12201,7 +12206,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:16">
+    <row r="2" s="2" customFormat="1" ht="36" spans="1:16">
       <c r="A2" s="2">
         <v>1000</v>
       </c>
@@ -12248,7 +12253,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:16">
+    <row r="3" s="2" customFormat="1" ht="36" spans="1:16">
       <c r="A3" s="2">
         <v>1001</v>
       </c>
@@ -12295,7 +12300,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:16">
+    <row r="4" s="2" customFormat="1" ht="36" spans="1:16">
       <c r="A4" s="2">
         <v>1002</v>
       </c>
@@ -12342,7 +12347,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:16">
+    <row r="5" s="2" customFormat="1" ht="36" spans="1:16">
       <c r="A5" s="2">
         <v>1003</v>
       </c>
@@ -12389,7 +12394,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:16">
+    <row r="6" s="2" customFormat="1" ht="36" spans="1:16">
       <c r="A6" s="2">
         <v>1004</v>
       </c>

--- a/config/PCS_125_英博.xlsx
+++ b/config/PCS_125_英博.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18519" windowHeight="11218" activeTab="1"/>
+    <workbookView windowWidth="22010" windowHeight="12332" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="遥测" sheetId="1" r:id="rId1"/>
@@ -1522,8 +1522,7 @@
     <t>{"en":"standby mode"}</t>
   </si>
   <si>
-    <t>0 停机|stop
-1 待机|standBy</t>
+    <t>1 待机|standBy</t>
   </si>
   <si>
     <t>运行状态</t>
@@ -12253,7 +12252,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="36" spans="1:16">
+    <row r="3" s="2" customFormat="1" spans="1:16">
       <c r="A3" s="2">
         <v>1001</v>
       </c>

--- a/config/PCS_125_英博.xlsx
+++ b/config/PCS_125_英博.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332" activeTab="1"/>
+    <workbookView windowWidth="18569" windowHeight="11268"/>
   </bookViews>
   <sheets>
     <sheet name="遥测" sheetId="1" r:id="rId1"/>
@@ -122,7 +122,7 @@
     <t>{"en":"PCS port C-phase voltage"}</t>
   </si>
   <si>
-    <t>PCS 端口 A 相电流</t>
+    <t>PCS 输出 A 相电流</t>
   </si>
   <si>
     <t>I16</t>
